--- a/content/pages.xlsx
+++ b/content/pages.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7362,7 +7362,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>topic-democracy</t>
+          <t>topic-beauty-and-art</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -7372,30 +7372,26 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Beauty and art</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>**Democracy** · hand-picked thoughts · [n] thoughts so far</t>
+          <t>**Beauty and art** · theme: Beauty and art · [n] thoughts so far</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>128,130,131,160,201,442,617,621</t>
-        </is>
-      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Beauty and art</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Should the people rule, and what keeps the many from going wrong?</t>
+          <t>Is beauty out there, or in the eye of the beholder?</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -7410,11 +7406,10 @@
       <c r="T77" s="2" t="inlineStr"/>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>**Athens and Plato (Ancient Greece).** Democracy began in Athens around 508 BCE. Citizens voted directly in an assembly, and many officials and jurors were chosen by lot. But only adult male citizens took part, perhaps one person in five or fewer: women, slaves, and foreigners were left out.
-Plato did not trust it. In his parable of the ship, the sailors fight over the helm, while the true pilot, who knows the winds and the stars, is mocked as a stargazer. He had seen a democratic jury sentence his teacher Socrates to death in 399 BCE.
-**Aristotle (Ancient Greece).** Aristotle was more open. A citizen, for him, is someone who takes turns governing and being governed, and a crowd can judge many things better than one person. Still, he feared rule by the many could turn into mob rule. He preferred a mixed government, held steady by a strong middle class.
-**Laozi (Taoists).** The *Tao Te Ching* looks at power from below. The best rulers are those the people hardly notice; worse ones are loved, then feared, then despised. Good government works quietly and lets people feel they did things themselves.
-**Rousseau and Mill (the Enlightenment and after).** Rousseau put the people at the heart of the state: when citizens stop caring about public affairs, the state is lost. Mill, a century later, saw a new danger. A majority can be a tyrant too, and silencing even one person who disagrees harms everyone. The phrase "tyranny of the majority" comes from Alexis de Tocqueville; Mill made it famous.</t>
+          <t>**Kenkō and Okakura (Japanese Aesthetics).** The Japanese writers love what is unfinished. Kenkō thought it better to leave a little imperfection, since perfect uniformity is dull. In *The Book of Tea*, Okakura says true beauty is found by the one who completes the incomplete in their own mind: what is left unsaid gives the viewer a part to play.
+**Hume (Enlightenment Ethics).** Hume started from the view that beauty is no quality in things, but exists in the mind that looks at them. Yet he did not leave it there. Some judgements are better than others, he argued, and the standard of taste is the shared verdict of rare, experienced, unprejudiced critics. Studying beauty, he added, softens the temper.
+**Laozi (Taoism).** The *Tao Te Ching* sees a hidden cost in naming beauty: as soon as everyone knows what is beautiful, they also know what is ugly. Each idea brings its opposite with it.
+**Nietzsche and Emerson (Existential Thought, Humanists and Essayists).** For Nietzsche, the greatest art is to "give style" to your own character, shaping strengths and weaknesses into one whole. Emerson saw in every work of genius our own rejected thoughts, coming back to us with a kind of borrowed majesty.</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr"/>
@@ -7422,16 +7417,14 @@
       <c r="X77" s="2" t="inlineStr"/>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>None of them trusts power without limits, whoever holds it. They split on whether ordinary people can be trusted to judge. Plato said no, Aristotle said often, and Mill said yes, but only with free speech protecting the few who disagree.</t>
+          <t>All of them link beauty to the person who sees it, not only to the object. They differ on how far. Hume searches for a standard that lets us say some tastes are better; the Japanese writers make the viewer a partner in the work; Nietzsche turns the art inward, onto how we shape our lives.</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr"/>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Athenian democracy": https://en.wikipedia.org/wiki/Athenian_democracy
-- Stanford Encyclopedia of Philosophy, "Aristotle's Political Theory": https://plato.stanford.edu/entries/aristotle-politics/ · "Plato's Ethics and Politics in The Republic": https://plato.stanford.edu/entries/plato-ethics-politics/ · Plato, Republic, Book VI (Jowett translation, Project Gutenberg): https://www.gutenberg.org/ebooks/1497
-- Wikipedia, "Tyranny of the majority": https://en.wikipedia.org/wiki/Tyranny_of_the_majority
-- The app's thoughts listed above, with their sources</t>
+          <t>- Stanford Encyclopedia of Philosophy, "Hume's Aesthetics": https://plato.stanford.edu/entries/hume-aesthetics/
+- The app's thoughts #177, #188, #259, #264, #421, #525, #533, and #534, with their sources</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -7441,7 +7434,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>Thinker and topic pages pilot</t>
+          <t>Theme pages, batch B</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr"/>
@@ -7449,7 +7442,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>topic-freedom</t>
+          <t>topic-change-and-impermanence</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -7459,34 +7452,26 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Change and impermanence</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>**Freedom** · theme: Freedom, choice, and intention, plus hand-picked thoughts · [n] thoughts so far</t>
+          <t>**Change and impermanence** · theme: Change and impermanence · [n] thoughts so far</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Freedom, choice, and intention</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>179,193,294,485,621,625</t>
-        </is>
-      </c>
+          <t>Change and impermanence</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Are you free when nobody stops you, or when you master yourself?</t>
+          <t>Everything changes, so how should we live with it?</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
@@ -7501,10 +7486,10 @@
       <c r="T78" s="2" t="inlineStr"/>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>**The Stoics and the East: freedom inside.** Epictetus taught that some things are in our power and others are not; freedom starts with knowing the difference. Spinoza called being ruled by your emotions a kind of bondage. Confucius said an army can lose its general, but nobody can take away the will of an ordinary person. Here, freedom is something no prison can remove.
-**Mill: freedom from others.** For Mill, the only freedom worth the name is to pursue your own good in your own way, as long as you do not stop others from doing the same. Over your own body and mind, you rule. Society may step in only to prevent harm to others. Yet Mill limited this to people "in the maturity of their faculties", and in the same chapter he called despotism legitimate over people he called "barbarians", if it improved them.
-**Rousseau and Locke: freedom with others.** Rousseau opens *The Social Contract* by saying people are born free and everywhere in chains. His answer is not fewer laws, but laws the people make together. Locke agrees that law, done well, does not restrain freedom but protects and enlarges it.
-**Wollstonecraft and Fuller: freedom for whom?** Both asked why freedom stopped at men. Wollstonecraft argued that blind obedience is what power wants, and education is the way out. Fuller wanted every path open to women as freely as to men.</t>
+          <t>**Heraclitus and Lucretius (Classical Greek Philosophy, Epicureanism).** Heraclitus said you cannot step into the same river twice, because new water is always flowing. Lucretius saw the same motion in matter itself: nothing comes from nothing, and nothing returns to nothing; things only break apart and form again.
+**The Dhammapada (Buddhist Philosophy).** For the *Dhammapada*, seeing clearly that all created things pass away is itself a path out of suffering. We suffer when we cling to what cannot last.
+**Epictetus and Marcus Aurelius (Stoicism).** Epictetus advised never saying "I have lost it", only "I have given it back": a child, a wife, an estate were only lent to us. Marcus Aurelius put it in five words: the universe is transformation.
+**Kenkō and Okakura (Japanese Aesthetics).** The Japanese writers find beauty in passing things. Kenkō asks whether we should look at the moon only when it is full, or at flowers only in full bloom. Okakura invites us to "dream of evanescence".</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr"/>
@@ -7512,15 +7497,13 @@
       <c r="X78" s="2" t="inlineStr"/>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>In 1958 the philosopher Isaiah Berlin named the split: "negative" freedom, being left alone, and "positive" freedom, being in control of your own life. Mill stands for the first, Rousseau for the second. Berlin warned that the second can be abused, when rulers claim to force people towards their "real" good. Liberals, in turn, would not call the Stoics' inner freedom real freedom at all.</t>
+          <t>All of them start from the same fact: nothing stays as it is. They differ on what to do with it. The Stoics accept it calmly; the Buddhist texts let go; the Japanese writers find beauty in it; Nietzsche goes further and welcomes change as the way we become new.</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr"/>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>- Stanford Encyclopedia of Philosophy, "Positive and Negative Liberty": https://plato.stanford.edu/entries/liberty-positive-negative/
-- John Stuart Mill, *On Liberty* (1859), chapter I (Project Gutenberg): https://www.gutenberg.org/ebooks/34901 · Wikipedia, "Negative liberty": https://en.wikipedia.org/wiki/Negative_liberty · Stanford Encyclopedia of Philosophy, 2014 version of the same entry (on the Stoics): https://plato.stanford.edu/archives/sum2014/entries/liberty-positive-negative/
-- The app's thoughts #15, #42, #168, #197, #198, and the others listed above, with their sources</t>
+          <t>- The app's thoughts #18, #33, #88, #121, #209, #345, #515, #517, and #529, with their sources</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
@@ -7530,7 +7513,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>Thinker and topic pages pilot</t>
+          <t>Theme pages, batch A</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr"/>
@@ -7538,7 +7521,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>topic-friendship</t>
+          <t>topic-character-and-virtue</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -7548,18 +7531,18 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Friendship</t>
+          <t>Character and virtue</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>**Friendship** · theme: Friendship and kindness · [n] thoughts so far</t>
+          <t>**Character and virtue** · theme: Character and virtue · [n] thoughts so far</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Friendship and kindness</t>
+          <t>Character and virtue</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
@@ -7567,7 +7550,7 @@
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>What makes someone a real friend, and why do we need them?</t>
+          <t>What makes a person good, and can you become one?</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
@@ -7582,10 +7565,10 @@
       <c r="T79" s="2" t="inlineStr"/>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>**Aristotle (Ancient Greece).** He saw three kinds of friendship: for usefulness, for pleasure, and for character. The first two fade when the use or the fun ends. Only the third lasts, because each friend loves who the other is. Such a friend, he says, is "another self", and good friends make each other better. He thought nobody would choose a life without friends, even with everything else.
-**Epicurus (Ancient Greece).** For Epicurus, friendship was the greatest help to a happy life, worth more than wealth or power. He lived it: his school, the Garden, was a community of friends outside politics, who shared meals and celebrations, and it welcomed women as students.
-**Confucius (Ancient China).** Friends help each other grow in virtue. A good friend tells you honestly when you are wrong, and does it with tact. But if the friend will not listen, you stop, rather than lose the friendship.
-**Montaigne (the Humanists).** After his friend Étienne de La Boétie died young, Montaigne wrote that true friendship cannot be explained: it happens between these two people, and no others. He believed such a friendship is so complete that a person can have only one, and that it is very rare. In the same essay he says women had never reached this kind of friendship, a view common among writers of his time.</t>
+          <t>**Aristotle (Classical Greek Philosophy).** Virtue, for Aristotle, is a settled trait of character, and you build it the way you learn a craft: by doing. We become just by doing just acts and brave by doing brave ones. Each virtue sits between two extremes, like courage between cowardice and recklessness. Hitting that middle point is hard, and it takes practical wisdom.
+**Confucius (Confucianism).** People start out much alike, Confucius said, and practice makes them grow far apart. The ideal is the "superior man", who asks a lot of himself and little of others, and who leads by example rather than by orders. Virtue is never lonely: whoever practises it will find neighbours.
+**The Dhammapada (Buddhist Philosophy).** The *Dhammapada* puts the work in each person's hands: by oneself evil is done, and by oneself it is left undone. Small good acts add up, like a water jar filling drop by drop. Anger is overcome by love, and evil by good.
+**Kant (Enlightenment Ethics).** Kant moved the focus from character to the will. Talents, courage, and even happiness can be used for bad ends; only a good will is good without qualification. Morality, he said, is not about how to be happy, but how to become worthy of happiness.</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr"/>
@@ -7593,17 +7576,15 @@
       <c r="X79" s="2" t="inlineStr"/>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>All four see friendship as one of the best things in life, and all link it to becoming a better person. They differ on numbers and reasons. Epicurus spoke openly of the safety and pleasure friends give; Aristotle cared most about friends valued for themselves; Montaigne thought the deepest kind happens only once. Nietzsche adds a sharper voice: a true friend should also challenge you.</t>
+          <t>All four say goodness takes effort and is not simply given at birth. They split on where it lives. For Aristotle and Confucius, it is a character shaped by long practice and good company; for Kant, it is the intention behind each act, done out of duty. Virtue ethics, the tradition of Aristotle and Confucius, faded in the West after the Enlightenment and returned in the late 1950s.</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr"/>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>- Stanford Encyclopedia of Philosophy, "Friendship": https://plato.stanford.edu/entries/friendship/
-- Wikipedia, "Epicurus": https://en.wikipedia.org/wiki/Epicurus
-- Cambridge University Library, "Of friendship" (Montaigne exhibition): https://wwwe.lib.cam.ac.uk/CUL/exhibitions/Montaigne/c3.html
-- Montaigne, "Of Friendship", Cotton translation (HyperEssays): https://hyperessays.net/essays/on-friendship/ · Wikipedia, "Michel de Montaigne": https://en.wikipedia.org/wiki/Michel_de_Montaigne
-- The app's thoughts #58, #112, #115, #117, #211, #280, #502, and #503, with their sources</t>
+          <t>- Stanford Encyclopedia of Philosophy, "Virtue Ethics": https://plato.stanford.edu/entries/ethics-virtue/
+- Stanford Encyclopedia of Philosophy, "Kant's Moral Philosophy": https://plato.stanford.edu/entries/kant-moral/ · "Confucius": https://plato.stanford.edu/entries/confucius/
+- The app's thoughts #109, #113, #119, #154, #155, #208, #328, #333, #339, #357, #475, #487, #492, #495, and #504, with their sources</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -7613,7 +7594,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>Thinker and topic pages pilot</t>
+          <t>Theme pages, batch A</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr"/>
@@ -7621,7 +7602,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>topic-justice</t>
+          <t>topic-death-and-mortality</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -7631,30 +7612,26 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Justice</t>
+          <t>Death and mortality</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>**Justice** · theme: Justice, power, and leadership · [n] thoughts so far</t>
+          <t>**Death and mortality** · theme: Death and mortality · [n] thoughts so far</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Justice, power, and leadership</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>Death and mortality</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>What do we owe each other, and who decides?</t>
+          <t>Should we think about death, and can we stop fearing it?</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
@@ -7669,10 +7646,10 @@
       <c r="T80" s="2" t="inlineStr"/>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>**Plato and Socrates (Ancient Greece).** In Plato's *Republic*, a character called Thrasymachus says justice is simply what serves the strong. Plato's answer is that justice is a kind of harmony: each part of a person, or of a city, doing its proper job. His teacher Socrates went further. He said it is better to suffer an injustice than to do one, and that we should never return harm for harm.
-**Aristotle (Ancient Greece).** For Aristotle, justice means giving people what they deserve, and good laws are reason without passion. A citizen is someone who takes turns ruling and being ruled. Yet the same book, the *Politics*, argues that some people are slaves by nature. Centuries later, this idea was used to defend the enslavement of Native Americans.
-**Epicurus (Ancient Greece).** Epicurus saw no justice written into nature. For him, justice is an agreement between people not to harm each other, and it can change from place to place. It still matters to the individual: the just person lives with the most peace of mind.
-**Confucius (Ancient China).** Justice begins with the people who lead. A ruler who acts rightly will be followed without needing many orders. When someone wrongs you, answer with justice, not with kindness or revenge. In classical Confucian thought, justice was a personal and public virtue, not a matter of law or equal rights.</t>
+          <t>**Epicurus and Lucretius (Epicureanism).** Epicurus argued that death is nothing to us: where death is, we are not, and where we are, death is not. Lucretius asked why we should not leave life like a guest leaving a banquet, full and content. On the day he died, in great pain, Epicurus wrote to a friend that the memory of their conversations outweighed it all.
+**Marcus Aurelius and Montaigne (Stoicism, Humanists and Essayists).** Marcus Aurelius reminded himself not to act as if he had ten thousand years. Montaigne took an old saying for an essay title: to study philosophy is to learn to die. Whoever has learned to die, he said, has unlearned how to be a slave.
+**Zhuangzi (Taoism).** When Zhuangzi's wife died, a friend found him beating on a bowl and singing. He had grieved like anyone, he explained, then saw her death as one more change, like spring turning to summer, autumn, and winter. Tagore says something close: death belongs to life as birth does.
+**Omar Khayyam and Kenkō (Persian and Sufi Poetry, Japanese Aesthetics).** For Khayyam, death is a door with no key and a veil no one sees past, so we should make the most of the days we have. Kenkō notes that death does not wait its turn like the seasons; it presses on us from behind.</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr"/>
@@ -7680,28 +7657,1906 @@
       <c r="X80" s="2" t="inlineStr"/>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>Most agree that justice is about more than rules: it shapes the kind of person you become. They split on where it comes from. For Plato it is part of how things should be; for Epicurus, and later for social contract thinkers like Rousseau, it is something people agree on. Modern debates add new questions the ancients rarely asked, such as how fair inequality can be, as in John Rawls's "veil of ignorance", or whether punishment should aim to repair harm.</t>
+          <t>Most of them say that facing death honestly makes life clearer and fear smaller. They split on how much to think about it. Montaigne and the Stoics advise keeping it in mind; Spinoza answered that a free person thinks of death least of all, and that wisdom is a meditation on life.</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr"/>
       <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>- The app's thoughts #4, #59, #73, #75, #170, #277, #387, #437, #520, #582, and #583, with their sources</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch B</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>topic-democracy</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Democracy</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>**Democracy** · hand-picked thoughts · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>128,130,131,160,201,442,617,621</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Should the people rule, and what keeps the many from going wrong?</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>**Athens and Plato (Classical Greek Philosophy).** Democracy began in Athens around 508 BCE. Citizens voted directly in an assembly, and many officials and jurors were chosen by lot. But only adult male citizens took part, perhaps one person in five or fewer: women, slaves, and foreigners were left out.
+Plato did not trust it. In his parable of the ship, the sailors fight over the helm, while the true pilot, who knows the winds and the stars, is mocked as a stargazer. He had seen a democratic jury sentence his teacher Socrates to death in 399 BCE.
+**Aristotle (Classical Greek Philosophy).** Aristotle was more open. A citizen, for him, is someone who takes turns governing and being governed, and a crowd can judge many things better than one person. Still, he feared rule by the many could turn into mob rule. He preferred a mixed government, held steady by a strong middle class.
+**Laozi (Taoism).** The *Tao Te Ching* looks at power from below. The best rulers are those the people hardly notice; worse ones are loved, then feared, then despised. Good government works quietly and lets people feel they did things themselves.
+**Rousseau and Mill (Enlightenment Ethics).** Rousseau put the people at the heart of the state: when citizens stop caring about public affairs, the state is lost. Mill, a century later, saw a new danger. A majority can be a tyrant too, and silencing even one person who disagrees harms everyone. The phrase "tyranny of the majority" comes from Alexis de Tocqueville; Mill made it famous.</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr"/>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>None of them trusts power without limits, whoever holds it. They split on whether ordinary people can be trusted to judge. Plato said no, Aristotle said often, and Mill said yes, but only with free speech protecting the few who disagree.</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>- Wikipedia, "Athenian democracy": https://en.wikipedia.org/wiki/Athenian_democracy
+- Stanford Encyclopedia of Philosophy, "Aristotle's Political Theory": https://plato.stanford.edu/entries/aristotle-politics/ · "Plato's Ethics and Politics in The Republic": https://plato.stanford.edu/entries/plato-ethics-politics/ · Plato, Republic, Book VI (Jowett translation, Project Gutenberg): https://www.gutenberg.org/ebooks/1497
+- Wikipedia, "Tyranny of the majority": https://en.wikipedia.org/wiki/Tyranny_of_the_majority
+- The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>Thinker and topic pages pilot</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>topic-desire-and-simplicity</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Desire and simplicity</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>**Desire and simplicity** · theme: Desire and simplicity · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Desire and simplicity</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Would we be happier wanting less?</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>**Epicurus (Epicureanism).** Epicurus sorted desires into three kinds: natural and necessary, like drinking when thirsty; natural but not necessary, like costly food; and neither, like statues in your honour. The first are easy to satisfy; the last have no limit. Nature's wealth, he said, is small and easy to get.
+**Marcus Aurelius, Epictetus, and Seneca (Stoicism).** Marcus Aurelius advised doing few things if you want peace of mind. Epictetus put it more bluntly: don't admire your clothes, and you won't be angry with the thief. Seneca noted that we fear everything as if we were mortal, and want everything as if we would live forever.
+**The Bhagavad Gita and the Dhammapada (Indian Philosophy, Buddhist Philosophy).** The *Gita* traces a chain: dwelling on things breeds attachment, attachment breeds desire, and desire breeds anger. Its answer is to act without clinging to the fruits of action. The *Dhammapada* says there is no fire like passion.
+**Laozi and Thoreau (Taoism, Humanists and Essayists).** For Laozi, there is no greater calamity than never being content. Many centuries later, Thoreau went to live by Walden Pond to keep only the essentials of life. His advice: "Simplify, simplify."</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr"/>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>Most agree that endless wanting makes us unhappy, and that it is better to change our desires than the world. Not everyone wants to drop desire, though. Émilie du Châtelet wrote that we are happy only through tastes and passions that are satisfied, and Simone Weil saw desire as what leads the mind.</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>- The app's thoughts #5, #25, #41, #61, #72, #182, #194, #254, #267, #268, #353, #368, #370, and #419, with their sources</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch A</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>topic-ego-pride-and-humility</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Ego, pride, and humility</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>**Ego, pride, and humility** · theme: Ego, pride, and humility · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Ego, pride, and humility</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>How much should we think of ourselves?</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>**Laozi (Taoism).** The *Tao Te Ching* praises water: it helps everything and settles in the low places others avoid. A cup filled to the brim is hard to carry. Knowing others is clever, it says, but knowing yourself is wisdom.
+**Confucius (Confucianism).** Confucius did not worry about being unknown, only about not knowing others. He noted that people of old studied to improve themselves, while people of his day studied to be seen. His students said he was free of four things, among them stubbornness and egoism.
+**Epictetus (Stoicism).** The first task of anyone who studies philosophy, said Epictetus, is to drop self-conceit, because nobody can learn what they think they already know. He also asked his students to remember how small a part of the whole they are.
+**La Rochefoucauld and Erasmus (Humanists and Essayists).** La Rochefoucauld called self-love the greatest of flatterers, and saw it behind even our virtues. In Erasmus's *Praise of Folly*, Folly herself admits that nothing is sillier than admiring yourself.</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr"/>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>All of them see pride as a blind spot that keeps us from learning and from seeing others clearly. They differ on the cure. Laozi, Confucius, and Epictetus think practice can make us humbler. La Rochefoucauld doubts we ever fully escape self-love; at best we learn to notice it.</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>- The app's thoughts #23, #44, #290, #301, #410, #411, #415, #468, #483, and #490, with their sources</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch A</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>topic-equality</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Equality</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>**Equality** · hand-picked thoughts · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>128,179,180,295,324,495,621,622</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Are people equal, and equal in what?</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>**Aristotle (Classical Greek Philosophy).** Aristotle gave the basic rule of fairness: treat like cases alike. Citizens, for him, took turns ruling and being ruled. But he did not think all people were alike: in the same book he argued that some are slaves by nature, an idea later used to defend slavery.
+**The Stoics and Confucius (Stoicism, Confucianism).** Other traditions stressed what we share. The Stoics taught the natural equality of all beings who have reason. Confucius said people are much alike by nature, and grow apart only by practice.
+**Rousseau (Enlightenment Ethics).** Rousseau opens *The Social Contract* by saying people are born free, yet everywhere they are in chains. In his earlier *Discourse on Inequality*, he traced social inequality to the first fences around land: we are lost, he warned, if we forget that the fruits belong to all and the earth to no one.
+**Wollstonecraft and Fuller (Enlightenment Ethics, Humanists and Essayists).** Both asked why equality stopped at men. Wollstonecraft argued that women seemed weaker only because they were denied education. Fuller noted that the self-reliance praised in her was called a fault in most women.</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr"/>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>Until the 18th century, most thinkers assumed people were unequal by nature; the idea of natural rights changed that. Today most agree people are equal in dignity. The open question is equal in what: rights, chances, or results. Rousseau worried about unequal property; Aristotle, even with his blind spots, about treating like cases alike.</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Equality": https://plato.stanford.edu/entries/equality/
+- Wikipedia, "Natural slavery": https://en.wikipedia.org/wiki/Natural_slavery · Stanford Encyclopedia of Philosophy, "Jean Jacques Rousseau": https://plato.stanford.edu/entries/rousseau/
+- The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>Society topic pages</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>topic-freedom</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>**Freedom** · theme: Freedom, choice, and intention, plus hand-picked thoughts · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Freedom, choice, and intention</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>179,193,294,485,621,625</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Are you free when nobody stops you, or when you master yourself?</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>**The Stoics and the East: freedom inside.** Epictetus taught that some things are in our power and others are not; freedom starts with knowing the difference. Spinoza called being ruled by your emotions a kind of bondage. Confucius said an army can lose its general, but nobody can take away the will of an ordinary person. Here, freedom is something no prison can remove.
+**Mill: freedom from others.** For Mill, the only freedom worth the name is to pursue your own good in your own way, as long as you do not stop others from doing the same. Over your own body and mind, you rule. Society may step in only to prevent harm to others. Yet Mill limited this to people "in the maturity of their faculties", and in the same chapter he called despotism legitimate over people he called "barbarians", if it improved them.
+**Rousseau and Locke: freedom with others.** Rousseau opens *The Social Contract* by saying people are born free and everywhere in chains. His answer is not fewer laws, but laws the people make together. Locke agrees that law, done well, does not restrain freedom but protects and enlarges it.
+**Wollstonecraft and Fuller: freedom for whom?** Both asked why freedom stopped at men. Wollstonecraft argued that blind obedience is what power wants, and education is the way out. Fuller wanted every path open to women as freely as to men.</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr"/>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>In 1958 the philosopher Isaiah Berlin named the split: "negative" freedom, being left alone, and "positive" freedom, being in control of your own life. Mill stands for the first, Rousseau for the second. Berlin warned that the second can be abused, when rulers claim to force people towards their "real" good. Liberals, in turn, would not call the Stoics' inner freedom real freedom at all.</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Positive and Negative Liberty": https://plato.stanford.edu/entries/liberty-positive-negative/
+- John Stuart Mill, *On Liberty* (1859), chapter I (Project Gutenberg): https://www.gutenberg.org/ebooks/34901 · Wikipedia, "Negative liberty": https://en.wikipedia.org/wiki/Negative_liberty · Stanford Encyclopedia of Philosophy, 2014 version of the same entry (on the Stoics): https://plato.stanford.edu/archives/sum2014/entries/liberty-positive-negative/
+- The app's thoughts #15, #42, #168, #197, #198, and the others listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>Thinker and topic pages pilot</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>topic-friendship-and-kindness</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Friendship and kindness</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>**Friendship and kindness** · theme: Friendship and kindness · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Friendship and kindness</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>What makes someone a real friend, and why do we need them?</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>**Aristotle (Classical Greek Philosophy).** He saw three kinds of friendship: for usefulness, for pleasure, and for character. The first two fade when the use or the fun ends. Only the third lasts, because each friend loves who the other is. Such a friend, he says, is "another self", and good friends make each other better. He thought nobody would choose a life without friends, even with everything else.
+**Epicurus (Epicureanism).** For Epicurus, friendship was the greatest help to a happy life, worth more than wealth or power. He lived it: his school, the Garden, was a community of friends outside politics, who shared meals and celebrations, and it welcomed women as students.
+**Confucius (Confucianism).** Friends help each other grow in virtue. A good friend tells you honestly when you are wrong, and does it with tact. But if the friend will not listen, you stop, rather than lose the friendship.
+**Montaigne (Humanists and Essayists).** After his friend Étienne de La Boétie died young, Montaigne wrote that true friendship cannot be explained: it happens between these two people, and no others. He believed such a friendship is so complete that a person can have only one, and that it is very rare. In the same essay he says women had never reached this kind of friendship, a view common among writers of his time.
+**Mencius (Confucianism).** Kindness, for Mencius, is in everyone from the start. Anyone who suddenly saw a child about to fall into a well would feel alarm and distress, he said, without thinking of reward. That feeling of compassion is the seed of goodness, and it only needs to grow.</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr"/>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>All of them see friendship and kindness as among the best things in life, and link them to becoming a better person. They differ on numbers and reasons. Epicurus spoke openly of the safety and pleasure friends give; Aristotle cared most about friends valued for themselves; Montaigne thought the deepest kind happens only once. Nietzsche adds a sharper voice: a true friend should also challenge you.</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Friendship": https://plato.stanford.edu/entries/friendship/
+- Wikipedia, "Epicurus": https://en.wikipedia.org/wiki/Epicurus
+- Cambridge University Library, "Of friendship" (Montaigne exhibition): https://wwwe.lib.cam.ac.uk/CUL/exhibitions/Montaigne/c3.html
+- Montaigne, "Of Friendship", Cotton translation (HyperEssays): https://hyperessays.net/essays/on-friendship/ · Wikipedia, "Michel de Montaigne": https://en.wikipedia.org/wiki/Michel_de_Montaigne
+- The app's thoughts #58, #112, #115, #117, #211, #280, #502, #503, #511, and #512, with their sources</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>Thinker and topic pages pilot</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>topic-habit-and-practice</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Habit and practice</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>**Habit and practice** · theme: Habit and practice · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Habit and practice</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Are we what we repeatedly do?</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>**Epictetus and Aristotle (Stoicism, Classical Greek Philosophy).** If you want to be a good reader, said Epictetus, read; if a writer, write. Nothing great happens suddenly, not even a grape or a fig. Aristotle said the same of goodness: we become just by doing just acts.
+**Confucius (Confucianism).** Confucius compared learning to building a mound, one basket of earth at a time. If you stop one basket short, the stopping is your own doing; if you add one basket, you have moved forward. People start out much alike; practice sets them apart.
+**The Dhammapada (Buddhist Philosophy).** The *Dhammapada* compares training the mind to a fletcher straightening an arrow. Small acts add up, like a water jar filling drop by drop, both for good and for bad. If you do something good, do it again, and take delight in it.
+**Laozi and Zhuangzi (Taoism).** Every great thing starts small: the journey of a thousand li begins with a single step. Zhuangzi's cook has used the same knife for nineteen years. After long practice he no longer sees the whole ox, and works with his mind, following the natural gaps.</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr"/>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>All of them see small, repeated acts as the way a person changes. They differ on the goal. Confucius and Epictetus speak of steady effort; Zhuangzi's cook shows effort turning into ease. Kenkō and Hume add a warning: habits and customs also hold us, and few things are harder to give up.</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>- The app's thoughts #22, #40, #109, #174, #311, #314, #338, #413, #432, #495, #514, and #527, with their sources</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch B</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>topic-happiness-and-the-good-life</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Happiness and the good life</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>**Happiness and the good life** · theme: Happiness and the good life · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Happiness and the good life</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>What does a good life need, and is happiness the point?</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>**Aristotle (Classical Greek Philosophy).** Happiness, for Aristotle, is the one thing we want for its own sake. His word, *eudaimonia*, means living well, or flourishing, not a passing mood. It is judged over a whole life: one swallow does not make a spring, and one good day does not make a happy life.
+**Epicurus (Epicureanism).** Epicurus made pleasure the goal, but not the pleasure of parties and luxury. He meant freedom from pain in the body and fear in the mind. Plain food, once hunger is gone, gives as much pleasure as a feast, and friends are the greatest help of all.
+**Confucius and the Dhammapada (Confucianism, Buddhist Philosophy).** Both find happiness in contentment. Confucius said he could still find joy with coarse rice, water, and his bent arm for a pillow. For the *Dhammapada*, health is the greatest gift and contentment the best riches.
+**Mill and Kant (Enlightenment Ethics).** Mill believed happiness is the goal, but some pleasures are higher than others: better to be Socrates dissatisfied than a fool satisfied. He also warned that happiness comes best on the side, while aiming at something else. Kant answered that morality is not about how to be happy, but how to become worthy of happiness.</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr"/>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>Most agree that happiness is not pleasure piled up, and that wanting less helps. They disagree on whether happiness is the aim of life. For Aristotle, Epicurus, and Mill it is, in different forms; for Kant, doing right comes first, whatever it costs.</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Aristotle's Ethics": https://plato.stanford.edu/entries/aristotle-ethics/
+- The app's thoughts #58, #64, #66, #67, #110, #116, #155, #158, #159, #331, and #479, with their sources</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch A</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>topic-justice</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Justice</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>**Justice** · theme: Justice, power, and leadership · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Justice, power, and leadership</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>What do we owe each other, and who decides?</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>**Plato and Socrates (Classical Greek Philosophy).** In Plato's *Republic*, a character called Thrasymachus says justice is simply what serves the strong. Plato's answer is that justice is a kind of harmony: each part of a person, or of a city, doing its proper job. His teacher Socrates went further. He said it is better to suffer an injustice than to do one, and that we should never return harm for harm.
+**Aristotle (Classical Greek Philosophy).** For Aristotle, justice means giving people what they deserve, and good laws are reason without passion. A citizen is someone who takes turns ruling and being ruled. Yet the same book, the *Politics*, argues that some people are slaves by nature. Centuries later, this idea was used to defend the enslavement of Native Americans.
+**Epicurus (Epicureanism).** Epicurus saw no justice written into nature. For him, justice is an agreement between people not to harm each other, and it can change from place to place. It still matters to the individual: the just person lives with the most peace of mind.
+**Confucius (Confucianism).** Justice begins with the people who lead. A ruler who acts rightly will be followed without needing many orders. When someone wrongs you, answer with justice, not with kindness or revenge. In classical Confucian thought, justice was a personal and public virtue, not a matter of law or equal rights.</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr"/>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>Most agree that justice is about more than rules: it shapes the kind of person you become. They split on where it comes from. For Plato it is part of how things should be; for Epicurus, and later for social contract thinkers like Rousseau, it is something people agree on. Modern debates add new questions the ancients rarely asked, such as how fair inequality can be, as in John Rawls's "veil of ignorance", or whether punishment should aim to repair harm.</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr">
         <is>
           <t>- Wikipedia, "Justice": https://en.wikipedia.org/wiki/Justice
 - Wikipedia, "Natural slavery": https://en.wikipedia.org/wiki/Natural_slavery · Stanford Encyclopedia of Philosophy, "Justice": https://plato.stanford.edu/entries/justice/ · "Epicurus": https://plato.stanford.edu/entries/epicurus/ · "Plato's Ethics and Politics in The Republic": https://plato.stanford.edu/entries/plato-ethics-politics/
 - The app's thoughts #71, #84, #85, #98, #127–129, #135, #491, #500, #504, and #617, with their sources</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
+      <c r="AB89" s="2" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
-      <c r="AC80" s="2" t="inlineStr">
+      <c r="AC89" s="2" t="inlineStr">
         <is>
           <t>Thinker and topic pages pilot</t>
         </is>
       </c>
-      <c r="AD80" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>topic-law-and-rights</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Law and rights</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>**Law and rights** · hand-picked thoughts · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>84,85,127,129,193,491,500,504,590,617,625</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Where do laws get their authority, and what rights do we have?</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>**Aristotle (Classical Greek Philosophy).** Is it better to be ruled by the best person or the best laws? Aristotle leaned towards laws, because even good rulers have passions that bend their judgement. The law, he said, is reason unaffected by desire. Without law and justice, the human being is the worst of animals.
+**Confucius (Confucianism).** Confucius trusted example more than rules. To govern means to correct, and a ruler who acts rightly is followed without giving orders. When wronged, repay injury with justice, and kindness with kindness.
+**Epicurus (Epicureanism).** Epicurus saw no justice written into nature. Justice is an agreement between people not to harm each other or be harmed, and it can differ from place to place and time to time.
+**Locke, Rousseau, and Wollstonecraft (Enlightenment Ethics).** Locke argued that all people have natural rights to life, liberty, and property, and that good law does not shrink freedom but protects and enlarges it. Rousseau wanted laws the people make together, and warned that a state is lost once citizens stop caring. Wollstonecraft demanded that rights include women.</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr"/>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>Most of them see good law as a defence against the passions of the powerful; Sa'di put it simply: a tyrant cannot govern, for no one expects the shepherd's duty from the wolf. They split on where law comes from. For Aristotle and Locke, it rests on reason and nature; for Epicurus, on agreement; for Confucius, it matters less than the ruler's character.</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Locke's Political Philosophy": https://plato.stanford.edu/entries/locke-political/ · "Aristotle's Political Theory": https://plato.stanford.edu/entries/aristotle-politics/
+- The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>Society topic pages</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>topic-learning-and-knowledge</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Learning and knowledge</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>**Learning and knowledge** · theme: Learning and knowledge · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Learning and knowledge</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>What is worth knowing, and how do we know that we know it?</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>**Socrates and Plato (Classical Greek Philosophy).** Socrates claimed one kind of wisdom: he did not think he knew what he didn't. He questioned people until they saw the limits of their own knowledge, which made him many enemies. For Plato, philosophy begins in wonder, and most of us are like prisoners in a cave, taking shadows for the real thing.
+**Confucius (Confucianism).** Confucius loved learning and said it should never stop. Learning without thinking is wasted, and thinking without learning is dangerous. Real knowledge means saying what you know and admitting what you don't. Anyone can teach you something: copy the good in people, and correct in yourself the bad you see in them.
+**Laozi and Zhuangzi (Taoism).** The Taoists doubted that more knowledge brings more wisdom. Learning adds something every day, but the Way is found by letting go, day by day. Zhuangzi adds that you cannot explain the ocean to a frog in a well: we all see from a narrow place.
+**Hume and Mill (Enlightenment Ethics).** Hume asked for less certainty and more evidence: a wise person matches belief to the evidence. Mill added that you only half know your own view if you have never heard the other side. Even a true belief, never challenged, turns into dead dogma.</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr"/>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>Nearly all of them start with humility: Socrates, Confucius, and Laozi all praise knowing the limits of what you know. They part ways on what to do next. Confucius and Mill say study and argue more; Laozi says empty your mind; Hume says follow the evidence and stay modest about the rest.</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Socrates": https://plato.stanford.edu/entries/socrates/ · "Laozi": https://plato.stanford.edu/entries/laozi/
+- The app's thoughts #96, #97, #104, #162, #167, #175, #418, #420, #429, #470, #471, #480, and #482, with their sources</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch A</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>topic-love</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>**Love** · theme: Love · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>What is love, and what does it ask of us?</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>**Plato (Classical Greek Philosophy).** In Plato's *Symposium*, guests at a dinner take turns praising love. One tells a myth: humans were once whole beings, cut in two, and love is the desire and pursuit of that lost whole. Then Socrates, quoting his teacher Diotima, describes love as a journey from one beautiful body towards ever purer beauty.
+**Rumi, Hafiz, and Ibn Arabi (Persian and Sufi Poetry).** For the Sufi poets, human love and love of God mirror each other. Love hurts, and the pain is the proof of it. Hafiz admits he thought love would be easy, then found it a hard road. Ibn Arabi wrote that a heart grown in love can take on every form.
+**Tagore and the Dhammapada (Indian Philosophy, Buddhist Philosophy).** Tagore saw love as the way we truly live in the world: when a person loves, giving becomes a joy, like a tree letting go of ripe fruit. The *Dhammapada* gives love a harder task: hatred never ends through hatred, only through love.
+**Dostoevsky (Existential Thought).** Dostoevsky saw how easy it is to love in theory. Love in action, says a monk in *The Brothers Karamazov*, is harsh and dreadful compared with love in dreams. The same monk tells of a doctor who found that the more he loved humanity in general, the less he loved people in particular.</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr"/>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>All of them see love as more than a feeling: it changes the one who loves. They differ on its object. Plato and the Sufi poets point beyond the person towards something higher; Dostoevsky and Montaigne bring it back to one real person, loved, as Montaigne said of his friend, "because it was he, because it was I".</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Plato's Aesthetics": https://plato.stanford.edu/entries/plato-aesthetics/
+- The app's thoughts #106, #219, #221, #280, #308, #378, #389, #559, #567, and #577, with their sources</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch B</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>topic-mind-and-emotions</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Mind and emotions</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>**Mind and emotions** · theme: Mind and emotions · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Mind and emotions</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Should we master our feelings, or listen to them?</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>**Marcus Aurelius (Stoicism).** For the Stoics, what upsets us is not the event but our judgement about it, and we can learn to judge differently. Marcus Aurelius notes that the mind takes on the colour of its habitual thoughts. The ideal Stoic is free of disturbing passions, though not of all feeling.
+**The Dhammapada (Buddhist Philosophy).** The *Dhammapada* opens with the claim that all we are comes from our thoughts. The mind is flighty and hard to hold, and taming it is the greatest good. Hatred never ends hatred; only love does.
+**Aristotle (Classical Greek Philosophy).** Aristotle did not want feelings gone, but right. Anyone can get angry. The skill is to be angry with the right person, to the right degree, at the right time, and for the right reason. A good character is one that feels the right amount.
+**Spinoza and Hume (Enlightenment Ethics).** Spinoza called being ruled by our emotions a kind of bondage, and said an emotion loses its grip once we understand it clearly. Hume turned the question around: reason on its own moves no one to act, and is, in his words, "the slave of the passions".</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr"/>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>Most of them believe the mind can be trained, and that much suffering comes from how we react. They disagree on the goal. The Stoics and the Buddhist texts aim to calm or uproot troubling passions; Aristotle wants feelings in the right measure; Hume, like Pascal with his "heart" that has its own reasons, gives feeling the leading role.</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr"/>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Stoicism": https://plato.stanford.edu/entries/stoicism/ · "Aristotle's Ethics": https://plato.stanford.edu/entries/aristotle-ethics/ · "Hume's Moral Philosophy": https://plato.stanford.edu/entries/hume-moral/
+- The app's thoughts #7, #9, #111, #168, #169, #173, #228, #307, #308, and #315, with their sources</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch A</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>topic-nature-and-the-universe</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Nature and the universe</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>**Nature and the universe** · theme: Nature and the universe · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Nature and the universe</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>What is the world made of, and where do we fit in it?</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>**Laozi and Zhuangzi (Taoism).** The Tao, the way of nature, cannot be fully named or explained. Its best image is water, which helps everything, takes the lowest place, and still wears away the hardest stone. A person lives well by following that way, not by forcing it.
+**Lucretius and Epicurus (Epicureanism).** For the Epicureans, everything is made of atoms moving in empty space; worlds form by chance, without any need for gods. Lucretius wrote that fear comes from not knowing the causes of things. Understanding nature, he said, is the cure for that fear.
+**Marcus Aurelius and Epictetus (Stoicism).** The Stoics saw the opposite: one living whole, shaped by reason, in which every part is connected. Marcus Aurelius told himself to see the universe as a single being with one substance and one soul. Epictetus reminded his students how small a part of it each of us is.
+**Kant and Pascal (Enlightenment Ethics, Existential Thought).** Two things filled Kant with ever-growing awe: the starry heavens above and the moral law within. Pascal saw human beings as reeds, the weakest thing in nature, but reeds that think, and our greatness lies in that thought.</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr"/>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>All of them say that understanding nature changes how we live in it. They split on whether it has a purpose. The Stoics see a rational order; the Epicureans see atoms and chance; the Taoists see a way that cannot be put into words. The Japanese writers add something simpler: notice it, from the dawn to the flowers.</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Lucretius": https://plato.stanford.edu/entries/lucretius/ · "Stoicism": https://plato.stanford.edu/entries/stoicism/
+- The app's thoughts #37, #44, #87, #89, #152, #226, #410, #422, #441, #543, and #553, with their sources</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch B</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>topic-purpose-and-meaning</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Purpose and meaning</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>**Purpose and meaning** · theme: Purpose and meaning · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Purpose and meaning</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>What is a life for?</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>**Aristotle (Classical Greek Philosophy).** Aristotle noticed that everything we do aims at some good, and those goods point to a final one: happiness, the thing we want for its own sake. For him, the question of meaning had an answer: a life of reason and virtue, lived well.
+**Tolstoy and William James (Existential Thought).** Tolstoy had fame, family, and wealth when his life "came to a standstill": he could no longer see what any of it was for. William James answered the same fear in a lecture called "Is Life Worth Living?". We live fully, he said, only by risking ourselves on what we believe.
+**Mill (Enlightenment Ethics).** At twenty, Mill asked himself whether reaching all his goals would make him happy, and an honest voice said no. He came out of the crisis with a lesson: happiness comes to those who aim at something other than their own happiness.
+**George Eliot, Dickinson, and Tagore (Humanists and Essayists, Indian Philosophy).** Many find meaning in what we do for others. "What do we live for," asks a character in *Middlemarch*, "if it is not to make life less difficult to each other?" Dickinson would not live in vain if she could stop one heart from breaking, and Tagore says we earn our life by giving it.</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr"/>
+      <c r="X95" s="2" t="inlineStr"/>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>Most of them say meaning comes from something larger than the self, whether virtue, a cause, or other people. They differ on whether it is given or made. Aristotle finds it in human nature; Nietzsche says you must become what you are; Zhuangzi gently mocks the whole idea, praising a useless tree that lives long because nobody wants it.</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>- The app's thoughts #116, #144, #163, #166, #214, #240, #243, #288, #296, #385, and #434, with their sources</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch B</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>topic-self-knowledge</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Self-knowledge</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>**Self-knowledge** · theme: Self-knowledge · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Self-knowledge</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Who are you, really, and can you ever know?</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>**Socrates (Classical Greek Philosophy).** At his trial, Socrates said the unexamined life is not worth living. For him, questioning yourself and others was not a hobby but a duty, worth dying for.
+**The Upanishads and the Buddhist texts (Indian Philosophy, Buddhist Philosophy).** The Upanishads look for a deep, lasting Self behind body and mind, and find it one with the Self in all beings. Buddhism turns this around. In *The Questions of King Milinda*, a chariot is just a name for its parts working together, and so is a person: there is no fixed self to find.
+**Confucius (Confucianism).** For Confucius, self-knowledge is daily practice. One of his students examined himself every day on three points: had he been loyal, been true to his friends, and practised what he was taught? The superior man looks for the cause of things in himself; the petty man looks for it in others.
+**Montaigne and La Rochefoucauld (Humanists and Essayists).** Montaigne made himself the subject of his *Essays*, because each person carries the whole human condition. La Rochefoucauld was less hopeful: we are so used to wearing masks for others that in the end we are disguised to ourselves.</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr"/>
+      <c r="X96" s="2" t="inlineStr"/>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>They all say the work begins inside, not in other people's opinions. They differ on what you find there: a lasting Self (the Upanishads), no fixed self at all (Buddhism), a self you still have to create (Nietzsche's "become what you are"), or a mirror of everyone (Montaigne).</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Socrates": https://plato.stanford.edu/entries/socrates/
+- The app's thoughts #95, #214, #273, #283, #355, #364, #366, #493, and #513, with their sources</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch A</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>topic-solitude-and-stillness</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Solitude and stillness</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>**Solitude and stillness** · theme: Solitude and stillness · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Solitude and stillness</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Why is it so hard to sit still, and what do we find when we do?</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>**Pascal (Existential Thought).** Pascal thought all human misfortune comes from one thing: we cannot stay quietly in a room. We chase distraction to avoid thinking about ourselves, and that distraction is itself our greatest misery.
+**Marcus Aurelius (Stoicism).** While ruling an empire, Marcus longed for a house in the country or by the sea, as rich Romans had. Then he reminded himself that he could retreat into his own mind whenever he chose, and that there is no quieter place.
+**Laozi and Zhuangzi (Taoism).** Muddy water, says the *Tao Te Ching*, becomes clear if you let it be still. Zhuangzi says the wise use the mind like a mirror: it grasps nothing and refuses nothing, and reflects what comes without holding on.
+**Kenkō and Chōmei (Japanese Aesthetics).** The Japanese recluses praised a quiet life away from the crowd. Kenkō asked how anyone could find leisure tiresome: free from cares, it is good simply to be alone. From his small hut, Chōmei watched the moon at his window and thought of people of old.</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr"/>
+      <c r="X97" s="2" t="inlineStr"/>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>All of them see stillness as the place where the mind clears. They differ on how alone to be. Schopenhauer and Nietzsche praise solitude itself, and the *Dhammapada* says it is better to travel alone than with a fool. For Marcus, though, the retreat is inward and can be taken anywhere, even in the middle of public life.</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>- The app's thoughts #3, #215, #225, #229, #230, #354, #417, #438, #522, and #541, with their sources</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch B</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>topic-suffering-and-resilience</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Suffering and resilience</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>**Suffering and resilience** · theme: Suffering and resilience · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Suffering and resilience</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>What do we do with pain we cannot avoid?</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>**Marcus Aurelius, Epictetus, and Boethius (Stoicism).** Marcus Aurelius asked to be like a headland that the waves keep breaking on, while it stands firm. Epictetus advised wishing for things to happen as they do, not as we would like. In prison, Boethius wrote that nothing is wretched unless we think it so.
+**Rumi and Hafiz (Persian and Sufi Poetry).** The Sufi poets see pain as part of the way. Rumi calls it a treasure that holds mercies, and the *Masnavi* opens with a reed flute crying for the reed bed it was cut from. Hafiz says no one reaches joy without passing through hardship.
+**Nietzsche and Dostoevsky (Existential Thought).** Nietzsche's answer was *amor fati*, love of fate: wanting nothing to be different, the hard parts included. Dostoevsky went further, calling suffering the origin of consciousness itself.
+**Weil and Mill (Existential Thought, Enlightenment Ethics).** Others look outward. Simone Weil said those who suffer need, above all, people able to pay them attention. And Mill believed most of the great causes of suffering can be reduced by human care and effort.</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr"/>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>Many of them say suffering can teach and deepen us, as Vivekananda put it: misery is sometimes a greater teacher than happiness. They differ on where the answer lies. The Stoics look to our own judgement, the Sufi poets to love and longing, Weil to other people, and Mill to changing the world itself.</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>- The app's thoughts #6, #17, #28, #199, #213, #236, #248, #380, #555, #570, and #596, with their sources</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch B</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>topic-time-and-the-present</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Time and the present</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>**Time and the present** · theme: Time and the present · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Time and the present</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Is life short, or do we waste it?</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>**Seneca (Stoicism).** Seneca argued that life is not short; we make it short by wasting it. How late, he said, to begin living just when we must leave. Epictetus added that he wanted to be present like the hour, and to pass like the hour.
+**Epicurus (Epicureanism).** Epicurus warned against putting off joy for a tomorrow we do not control. The future is neither fully ours nor fully out of our hands. And remembering the good days we have had is part of a happy life.
+**Omar Khayyam and Hafiz (Persian and Sufi Poetry).** The Persian poets feel time slipping past. Khayyam's "Moving Finger" writes and moves on, and nothing can make it go back. Their answer is to make the most of the days we have.
+**Kenkō and Pascal (Japanese Aesthetics, Existential Thought).** Kenkō noted that the seasons come in order, but death comes when it likes, so we should not put off what matters. Pascal saw the same habit from another side: we never live, but only hope to live.</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr"/>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>All of them say the present is the only time we truly have. They differ on what to fill it with: pleasure and wine for Khayyam, wisdom and duty for Seneca, quiet attention for Kenkō. Montaigne sums up the common ground: life is measured by its use, not its length.</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>- The app's thoughts #24, #26, #43, #63, #77, #79, #227, #278, #520, #579, and #583, with their sources</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch A</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>topic-tolerance</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>**Tolerance** · hand-picked thoughts · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>160,201,550,577,613,614,624</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>How do we live with people who believe differently?</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>**Locke (Enlightenment Ethics).** In *A Letter Concerning Toleration* (1689), Locke argued that faith cannot be forced, so the state should not try. Churches are voluntary groups, and religion is a matter for each person. But his tolerance had limits: he refused it to atheists, whose promises he thought could not be trusted, and to churches whose members owed loyalty to a foreign ruler.
+**Voltaire (Enlightenment Ethics).** After a Protestant merchant, Jean Calas, was executed in Toulouse in 1762 on a false charge, Voltaire wrote his *Treatise on Tolerance*. In his *Philosophical Dictionary* he calls tolerance the mark of our humanity: we are all made of weakness and error, so let us forgive each other's foolishness. Prejudice, he adds, is an opinion without judgement, taught to children before they can think.
+**Mill (Enlightenment Ethics).** Mill moved the question from religion to every kind of opinion. If all of humanity but one person agreed, they would have no more right to silence that person than the one would have to silence them. Silencing a view, he said, assumes we cannot be wrong.
+**Ibn Arabi and Okakura (Persian and Sufi Poetry, Japanese Aesthetics).** Ibn Arabi wrote of a heart that can take on every form: a monastery, a temple, a place of pilgrimage. Okakura, writing in English for Western readers, said East and West had grown along different lines, with no reason why one should not complete the other.</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr"/>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>All of them see that forcing belief does not work and that our own views may be wrong. They disagree on the limits. Locke still excluded some groups; Voltaire mostly had religious violence in mind; Mill defended almost any opinion, short of harm to others.</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>- Stanford Encyclopedia of Philosophy, "Toleration": https://plato.stanford.edu/entries/toleration/
+- Wikipedia, "A Letter Concerning Toleration": https://en.wikipedia.org/wiki/A_Letter_Concerning_Toleration · "Treatise on Tolerance": https://en.wikipedia.org/wiki/Treatise_on_Tolerance
+- The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>Society topic pages</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>topic-war-and-peace</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>War and peace</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>**War and peace** · hand-picked thoughts · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>310,330,452,592,616,623</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Can war ever be right, and what makes peace last?</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>**Laozi and the Dhammapada (Taoism, Buddhist Philosophy).** The *Tao Te Ching* says the most skilled warrior shows no warlike look and never gives way to rage. The *Dhammapada* sees what victory costs: it breeds hatred, because the loser is unhappy. And the greatest victory is over yourself, not over a thousand armies.
+**The Bhagavad Gita (Indian Philosophy).** The *Gita* is set on a battlefield. Prince Arjuna sees relatives, friends, and teachers in the enemy ranks, drops his bow, and refuses to fight. Krishna urges him to do his duty as a warrior. Yet Gandhi learned the last verses of its second chapter by heart and kept them as a companion in his non-violent movement.
+**Hobbes and Kant (Enlightenment Ethics).** Hobbes, who lived through civil war, described life without government as a war of all against all. Peace, for him, needs a strong ruler; a commonwealth, he wrote, is the mother of peace. Kant hoped for more: in *Towards Perpetual Peace* (1795) he proposed republics joined in a union of states.
+**Voltaire and Tolstoy (Enlightenment Ethics, Existential Thought).** Voltaire noted a sad truth: wishing your country to be great usually means wishing harm on your neighbours. Tolstoy went furthest: read literally, he said, the Sermon on the Mount forbids resisting evil by force. His ideas on non-violence deeply impressed Gandhi.</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr"/>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>None of them see war as glorious in itself. They split on whether it can be justified. The *Gita* accepts a just duty to fight, and Hobbes and Kant seek peace through political order; Tolstoy rejects violence altogether. Sa'di adds a quieter thought: a falsehood that brings peace can be better than a truth that stirs up harm.</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>- Wikipedia, "Bhagavad Gita": https://en.wikipedia.org/wiki/Bhagavad_Gita · "The Kingdom of God Is Within You": https://en.wikipedia.org/wiki/The_Kingdom_of_God_Is_Within_You
+- Stanford Encyclopedia of Philosophy, "Hobbes's Moral and Political Philosophy": https://plato.stanford.edu/entries/hobbes-moral/ · "Kant's Social and Political Philosophy": https://plato.stanford.edu/entries/kant-social-political/
+- The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>Society topic pages</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>topic-work-and-action</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Work and action</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>**Work and action** · theme: Work and action · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Work and action</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>How should we act, and what should we expect from it?</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>**The Bhagavad Gita and Vivekananda (Indian Philosophy).** In the *Gita*, Krishna tells Arjuna that his business is with the action alone, never with its fruits. It is better to do your own task imperfectly than someone else's well. Vivekananda put it simply: work without stopping, but without attachment.
+**Marcus Aurelius (Stoicism).** Even an emperor found it hard to get up in the morning. His reminder to himself: I am rising to do the work of a human being. He also told himself to stop talking about what a good man should be, and simply be one.
+**Laozi and Zhuangzi (Taoism).** The Taoists value action that does not force. Governing a great state, says the *Tao Te Ching*, is like cooking small fish: stir too much and they fall apart. Zhuangzi's cook works with the grain of things, and his knife stays sharp for nineteen years.
+**Confucius and Voltaire (Confucianism, Enlightenment Ethics).** Confucius praised the person who acts first and speaks afterwards. At the end of Voltaire's *Candide*, after war, shipwreck, and earthquake, the hero stops arguing about whether all is for the best. "We must cultivate our garden."</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr"/>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>All of them trust deeds over words. They differ on effort and reward. The *Gita* and the Stoics speak of duty done well whatever the result; the Taoists warn against forcing things; Voltaire suggests that useful work close to home may be the best answer to questions we cannot solve.</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>- The app's thoughts #10, #12, #360, #368, #381, #432, #449, #472, and #611, with their sources</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>Theme pages, batch B</t>
+        </is>
+      </c>
+      <c r="AD102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>topic-work-and-wealth</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Work and wealth</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>**Work and wealth** · hand-picked thoughts · [n] thoughts so far</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>12,61,184,252,406,479,489,521,575,622</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>How much is enough, and what is work for?</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>**Epicurus and Marcus Aurelius (Epicureanism, Stoicism).** Epicurus said nature's wealth is limited and easy to get, while the wealth of empty wishes has no end. Marcus Aurelius, emperor of Rome, reminded himself each morning that he was rising to do the work of a human being.
+**Confucius and Sa'di (Confucianism, Persian and Sufi Poetry).** Confucius could find joy with coarse rice and water, and called riches gained by wrongdoing a floating cloud. Being poor without complaining is hard, he said; being rich without pride is easy. Sa'di advised anyone who wants riches to ask for contentment instead.
+**Adam Smith and Rousseau (Enlightenment Ethics).** Adam Smith argued in *The Wealth of Nations* that wealth grows through free exchange and the division of labour, as if guided by an "invisible hand". Yet his first book began with sympathy: however selfish we are, we care about others' happiness. Rousseau saw a darker side: the first person who fenced off land, said "This is mine", and found people simple enough to believe it, opened the way to crimes, wars, and misery.
+**Vivekananda and Schopenhauer (Indian Philosophy, Existential Thought).** Vivekananda taught that the best work is done for no reward, neither money nor fame. Schopenhauer compared riches to sea water: the more you drink, the thirstier you get.</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr"/>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>Most of them warn that wealth beyond need rarely brings peace. They differ on what wealth does for society. Smith saw trade and work as the way whole nations grow richer; Rousseau saw property as the root of inequality; the Stoics and the *Gita* tradition care less about the wealth than about the spirit in which we work.</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>- Wikipedia, "The Wealth of Nations": https://en.wikipedia.org/wiki/The_Wealth_of_Nations · Stanford Encyclopedia of Philosophy, "Adam Smith's Moral and Political Philosophy": https://plato.stanford.edu/entries/smith-moral-political/
+- The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>Society topic pages</t>
+        </is>
+      </c>
+      <c r="AD103" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7714,7 +9569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C253"/>
+  <dimension ref="A1:C304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11363,377 +13218,1152 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>topic-democracy</t>
+          <t>topic-beauty-and-art</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Wikipedia, "Athenian democracy"</t>
+          <t>Stanford Encyclopedia of Philosophy, "Hume's Aesthetics"</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Athenian_democracy</t>
+          <t>https://plato.stanford.edu/entries/hume-aesthetics/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>topic-democracy</t>
+          <t>topic-beauty-and-art</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Stanford Encyclopedia of Philosophy, "Aristotle's Political Theory"</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/aristotle-politics/</t>
-        </is>
-      </c>
+          <t>The app's thoughts #177, #188, #259, #264, #421, #525, #533, and #534, with their sources</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>topic-democracy</t>
+          <t>topic-change-and-impermanence</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>"Plato's Ethics and Politics in The Republic"</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/plato-ethics-politics/</t>
-        </is>
-      </c>
+          <t>The app's thoughts #18, #33, #88, #121, #209, #345, #515, #517, and #529, with their sources</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>topic-democracy</t>
+          <t>topic-character-and-virtue</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Plato, Republic, Book VI (Jowett translation, Project Gutenberg)</t>
+          <t>Stanford Encyclopedia of Philosophy, "Virtue Ethics"</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://www.gutenberg.org/ebooks/1497</t>
+          <t>https://plato.stanford.edu/entries/ethics-virtue/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>topic-democracy</t>
+          <t>topic-character-and-virtue</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Wikipedia, "Tyranny of the majority"</t>
+          <t>Stanford Encyclopedia of Philosophy, "Kant's Moral Philosophy"</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tyranny_of_the_majority</t>
+          <t>https://plato.stanford.edu/entries/kant-moral/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>topic-democracy</t>
+          <t>topic-character-and-virtue</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>The app's thoughts listed above, with their sources</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
+          <t>"Confucius"</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/confucius/</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>topic-freedom</t>
+          <t>topic-character-and-virtue</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Stanford Encyclopedia of Philosophy, "Positive and Negative Liberty"</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/liberty-positive-negative/</t>
-        </is>
-      </c>
+          <t>The app's thoughts #109, #113, #119, #154, #155, #208, #328, #333, #339, #357, #475, #487, #492, #495, and #504, with their sources</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>topic-freedom</t>
+          <t>topic-death-and-mortality</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>John Stuart Mill, *On Liberty* (1859), chapter I (Project Gutenberg)</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>https://www.gutenberg.org/ebooks/34901</t>
-        </is>
-      </c>
+          <t>The app's thoughts #4, #59, #73, #75, #170, #277, #387, #437, #520, #582, and #583, with their sources</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>topic-freedom</t>
+          <t>topic-democracy</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Wikipedia, "Negative liberty"</t>
+          <t>Wikipedia, "Athenian democracy"</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Negative_liberty</t>
+          <t>https://en.wikipedia.org/wiki/Athenian_democracy</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>topic-freedom</t>
+          <t>topic-democracy</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Stanford Encyclopedia of Philosophy, 2014 version of the same entry (on the Stoics)</t>
+          <t>Stanford Encyclopedia of Philosophy, "Aristotle's Political Theory"</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://plato.stanford.edu/archives/sum2014/entries/liberty-positive-negative/</t>
+          <t>https://plato.stanford.edu/entries/aristotle-politics/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>topic-freedom</t>
+          <t>topic-democracy</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>The app's thoughts #15, #42, #168, #197, #198, and the others listed above, with their sources</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr"/>
+          <t>"Plato's Ethics and Politics in The Republic"</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/plato-ethics-politics/</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>topic-friendship</t>
+          <t>topic-democracy</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Stanford Encyclopedia of Philosophy, "Friendship"</t>
+          <t>Plato, Republic, Book VI (Jowett translation, Project Gutenberg)</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://plato.stanford.edu/entries/friendship/</t>
+          <t>https://www.gutenberg.org/ebooks/1497</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>topic-friendship</t>
+          <t>topic-democracy</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Wikipedia, "Epicurus"</t>
+          <t>Wikipedia, "Tyranny of the majority"</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Epicurus</t>
+          <t>https://en.wikipedia.org/wiki/Tyranny_of_the_majority</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>topic-friendship</t>
+          <t>topic-democracy</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Cambridge University Library, "Of friendship" (Montaigne exhibition)</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>https://wwwe.lib.cam.ac.uk/CUL/exhibitions/Montaigne/c3.html</t>
-        </is>
-      </c>
+          <t>The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>topic-friendship</t>
+          <t>topic-desire-and-simplicity</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Montaigne, "Of Friendship", Cotton translation (HyperEssays)</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>https://hyperessays.net/essays/on-friendship/</t>
-        </is>
-      </c>
+          <t>The app's thoughts #5, #25, #41, #61, #72, #182, #194, #254, #267, #268, #353, #368, #370, and #419, with their sources</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>topic-friendship</t>
+          <t>topic-ego-pride-and-humility</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Wikipedia, "Michel de Montaigne"</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Michel_de_Montaigne</t>
-        </is>
-      </c>
+          <t>The app's thoughts #23, #44, #290, #301, #410, #411, #415, #468, #483, and #490, with their sources</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>topic-friendship</t>
+          <t>topic-equality</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>The app's thoughts #58, #112, #115, #117, #211, #280, #502, and #503, with their sources</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr"/>
+          <t>Stanford Encyclopedia of Philosophy, "Equality"</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/equality/</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>topic-justice</t>
+          <t>topic-equality</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Wikipedia, "Justice"</t>
+          <t>Wikipedia, "Natural slavery"</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Justice</t>
+          <t>https://en.wikipedia.org/wiki/Natural_slavery</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>topic-justice</t>
+          <t>topic-equality</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Wikipedia, "Natural slavery"</t>
+          <t>Stanford Encyclopedia of Philosophy, "Jean Jacques Rousseau"</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Natural_slavery</t>
+          <t>https://plato.stanford.edu/entries/rousseau/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>topic-justice</t>
+          <t>topic-equality</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Stanford Encyclopedia of Philosophy, "Justice"</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/justice/</t>
-        </is>
-      </c>
+          <t>The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>topic-justice</t>
+          <t>topic-freedom</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>"Epicurus"</t>
+          <t>Stanford Encyclopedia of Philosophy, "Positive and Negative Liberty"</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://plato.stanford.edu/entries/epicurus/</t>
+          <t>https://plato.stanford.edu/entries/liberty-positive-negative/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>topic-justice</t>
+          <t>topic-freedom</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>"Plato's Ethics and Politics in The Republic"</t>
+          <t>John Stuart Mill, *On Liberty* (1859), chapter I (Project Gutenberg)</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://plato.stanford.edu/entries/plato-ethics-politics/</t>
+          <t>https://www.gutenberg.org/ebooks/34901</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
+          <t>topic-freedom</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Wikipedia, "Negative liberty"</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Negative_liberty</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>topic-freedom</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, 2014 version of the same entry (on the Stoics)</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/archives/sum2014/entries/liberty-positive-negative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>topic-freedom</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>The app's thoughts #15, #42, #168, #197, #198, and the others listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>topic-friendship-and-kindness</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Friendship"</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/friendship/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>topic-friendship-and-kindness</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Wikipedia, "Epicurus"</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Epicurus</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>topic-friendship-and-kindness</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Cambridge University Library, "Of friendship" (Montaigne exhibition)</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>https://wwwe.lib.cam.ac.uk/CUL/exhibitions/Montaigne/c3.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>topic-friendship-and-kindness</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Montaigne, "Of Friendship", Cotton translation (HyperEssays)</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>https://hyperessays.net/essays/on-friendship/</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>topic-friendship-and-kindness</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Wikipedia, "Michel de Montaigne"</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Michel_de_Montaigne</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>topic-friendship-and-kindness</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>The app's thoughts #58, #112, #115, #117, #211, #280, #502, #503, #511, and #512, with their sources</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>topic-habit-and-practice</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>The app's thoughts #22, #40, #109, #174, #311, #314, #338, #413, #432, #495, #514, and #527, with their sources</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>topic-happiness-and-the-good-life</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Aristotle's Ethics"</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/aristotle-ethics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>topic-happiness-and-the-good-life</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>The app's thoughts #58, #64, #66, #67, #110, #116, #155, #158, #159, #331, and #479, with their sources</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
           <t>topic-justice</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Wikipedia, "Justice"</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>topic-justice</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Wikipedia, "Natural slavery"</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Natural_slavery</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>topic-justice</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Justice"</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/justice/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>topic-justice</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>"Epicurus"</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/epicurus/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>topic-justice</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>"Plato's Ethics and Politics in The Republic"</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/plato-ethics-politics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>topic-justice</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
         <is>
           <t>The app's thoughts #71, #84, #85, #98, #127–129, #135, #491, #500, #504, and #617, with their sources</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>topic-law-and-rights</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Locke's Political Philosophy"</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/locke-political/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>topic-law-and-rights</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>"Aristotle's Political Theory"</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/aristotle-politics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>topic-law-and-rights</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>topic-learning-and-knowledge</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Socrates"</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/socrates/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>topic-learning-and-knowledge</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>"Laozi"</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/laozi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>topic-learning-and-knowledge</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>The app's thoughts #96, #97, #104, #162, #167, #175, #418, #420, #429, #470, #471, #480, and #482, with their sources</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>topic-love</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Plato's Aesthetics"</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/plato-aesthetics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>topic-love</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>The app's thoughts #106, #219, #221, #280, #308, #378, #389, #559, #567, and #577, with their sources</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>topic-mind-and-emotions</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Stoicism"</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/stoicism/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>topic-mind-and-emotions</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>"Aristotle's Ethics"</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/aristotle-ethics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>topic-mind-and-emotions</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>"Hume's Moral Philosophy"</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/hume-moral/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>topic-mind-and-emotions</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>The app's thoughts #7, #9, #111, #168, #169, #173, #228, #307, #308, and #315, with their sources</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>topic-nature-and-the-universe</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Lucretius"</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/lucretius/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>topic-nature-and-the-universe</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>"Stoicism"</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/stoicism/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>topic-nature-and-the-universe</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>The app's thoughts #37, #44, #87, #89, #152, #226, #410, #422, #441, #543, and #553, with their sources</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>topic-purpose-and-meaning</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>The app's thoughts #116, #144, #163, #166, #214, #240, #243, #288, #296, #385, and #434, with their sources</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>topic-self-knowledge</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Socrates"</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/socrates/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>topic-self-knowledge</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>The app's thoughts #95, #214, #273, #283, #355, #364, #366, #493, and #513, with their sources</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>topic-solitude-and-stillness</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>The app's thoughts #3, #215, #225, #229, #230, #354, #417, #438, #522, and #541, with their sources</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>topic-suffering-and-resilience</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>The app's thoughts #6, #17, #28, #199, #213, #236, #248, #380, #555, #570, and #596, with their sources</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>topic-time-and-the-present</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>The app's thoughts #24, #26, #43, #63, #77, #79, #227, #278, #520, #579, and #583, with their sources</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>topic-tolerance</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Toleration"</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/toleration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>topic-tolerance</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Wikipedia, "A Letter Concerning Toleration"</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/A_Letter_Concerning_Toleration</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>topic-tolerance</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>"Treatise on Tolerance"</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Treatise_on_Tolerance</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>topic-tolerance</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>topic-war-and-peace</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Wikipedia, "Bhagavad Gita"</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bhagavad_Gita</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>topic-war-and-peace</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>"The Kingdom of God Is Within You"</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Kingdom_of_God_Is_Within_You</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>topic-war-and-peace</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Hobbes's Moral and Political Philosophy"</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/hobbes-moral/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>topic-war-and-peace</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>"Kant's Social and Political Philosophy"</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/kant-social-political/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>topic-war-and-peace</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>topic-work-and-action</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>The app's thoughts #10, #12, #360, #368, #381, #432, #449, #472, and #611, with their sources</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>topic-work-and-wealth</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Wikipedia, "The Wealth of Nations"</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Wealth_of_Nations</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>topic-work-and-wealth</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Stanford Encyclopedia of Philosophy, "Adam Smith's Moral and Political Philosophy"</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/smith-moral-political/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>topic-work-and-wealth</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>The app's thoughts listed above, with their sources</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content/pages.xlsx
+++ b/content/pages.xlsx
@@ -786,7 +786,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>history, context, history of mentalities</t>
+          <t>history of mentalities, history, context</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -873,7 +873,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Athens, ancient Greece, Greeks, classical antiquity</t>
+          <t>Athens, city-states, classical antiquity, Hellenistic, Greeks</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -986,7 +986,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Rome, Roman Empire, Romans, antiquity</t>
+          <t>Roman Empire, Augustus, Pax Romana, slavery, Christianity, Romans</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ancient China, Warring States, Zhou, Hundred Schools</t>
+          <t>Warring States, Zhou dynasty, Qin, Hundred Schools, Mandate of Heaven, ancient China</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>ancient India, Vedas, Buddha, shramanas</t>
+          <t>Vedas, Buddha, shramanas, caste, Indo-Greeks</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -1343,7 +1343,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Islamic world, Persia, Baghdad, Islamic Golden Age, Mongols</t>
+          <t>Baghdad, Persia, Seljuks, Mongols, Islamic Golden Age, Sufis</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Heian, Kamakura, samurai, medieval Japan</t>
+          <t>Heian, Kamakura, samurai, court women, mappō, medieval Japan</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Renaissance, humanism, Reformation, Black Death</t>
+          <t>humanism, Black Death, printing, Reformation, Florence, wars of religion</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17th century, Thirty Years' War, Scientific Revolution, wars of religion</t>
+          <t>Thirty Years' War, Scientific Revolution, wars of religion, English Civil War, Galileo</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Enlightenment, Age of Reason, 18th century, philosophes</t>
+          <t>Age of Reason, 18th century, philosophes, salons, Encyclopédie, slave trade</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1937,7 +1937,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19th century, Industrial Revolution, Russia, Victorian</t>
+          <t>Industrial Revolution, 1848, serfdom, Victorian, Darwin</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -2059,7 +2059,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>America, United States, Transcendentalism, abolition</t>
+          <t>United States, Transcendentalism, slavery, abolition, Civil War, Seneca Falls</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -2180,7 +2180,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>colonialism, British India, Meiji Japan, East and West</t>
+          <t>colonialism, British India, Meiji Japan, East and West, Parliament of Religions</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>world wars, 20th century, First World War, Second World War, Holocaust</t>
+          <t>First World War, Second World War, Holocaust, 20th century, world wars</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Buddhism, Buddha, nirvana, mindfulness</t>
+          <t>Buddha, nirvana, not-self, mindfulness, Dhamma, impermanence</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>ancient Greek philosophy, Socrates, virtue, eudaimonia</t>
+          <t>Socrates, eudaimonia, virtue, the soul, Athens</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>ritual, filial piety, junzi, the Way</t>
+          <t>junzi, ren, ritual, filial piety, Analects, the mean</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Enlightenment, reason, rights, utilitarianism</t>
+          <t>Enlightenment, reason, rights, utilitarianism, categorical imperative, social contract</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Enlightenment, Utilitarianism, utilitarian</t>
+          <t>Utilitarianism, utilitarian</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>pleasure, ataraxia, friendship, atoms</t>
+          <t>ataraxia, pleasure, the Garden, atoms, friendship</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>existentialism, meaning, anxiety, the absurd</t>
+          <t>existentialism, meaning, anxiety, the absurd, God is dead</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>humanism, essays, Renaissance, moralists</t>
+          <t>humanism, essays, moralists, maxims, Renaissance, Transcendentalism</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Hinduism, Vedanta, Upanishads, yoga</t>
+          <t>Vedanta, Atman, Brahman, karma, dharma, yoga, Hinduism</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>emptiness, imperfection, seasons, wabi-sabi, mono no aware, tea ceremony, Zen</t>
+          <t>wabi-sabi, mono no aware, tea ceremony, Zen, imperfection, emptiness, seasons</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
@@ -3414,7 +3414,7 @@
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>heart, divine love, halting-station, wine, Sufism, mysticism, ghazal</t>
+          <t>Sufism, divine love, ghazal, mysticism, nafs, wine, heart, halting-station</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>tranquillity, Stoics, virtue, what is in our control, resilience</t>
+          <t>what is in our control, virtue, tranquillity, resilience, memento mori, Stoics</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>softness, water, Tao, the Way, wu wei</t>
+          <t>Tao, wu wei, the Way, water, softness, emptiness</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>sympathy, The Theory of Moral Sentiments</t>
+          <t>The Theory of Moral Sentiments, The Wealth of Nations, sympathy</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
@@ -4082,7 +4082,7 @@
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>boredom, Parerga and Paralipomena</t>
+          <t>Parerga and Paralipomena, boredom, pessimism, the will</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>diversion, the heart's reasons, Pensées</t>
+          <t>Pensées, the heart's reasons, diversion</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>mean man, superior man, reciprocity, the mean, Analects</t>
+          <t>Analects, superior man, reciprocity, the mean, ren, mean man</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>custom, A Treatise of Human Nature, An Enquiry Concerning Human Understanding</t>
+          <t>A Treatise of Human Nature, An Enquiry Concerning Human Understanding, custom, bundle of perceptions</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Diderot effect, Philosophical Thoughts, Regrets on My Old Dressing Gown</t>
+          <t>Encyclopédie, Philosophical Thoughts, Regrets on My Old Dressing Gown, Diderot effect</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Discourses, Enchiridion</t>
+          <t>Enchiridion, Discourses, what is in our power</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>The Garden, Principal Doctrines, Letter to Menoeceus, Vatican Sayings</t>
+          <t>Letter to Menoeceus, Principal Doctrines, The Garden, Vatican Sayings, ataraxia, pleasure</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
@@ -5416,7 +5416,7 @@
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>become who you are, Thus Spake Zarathustra, Beyond Good and Evil, The Joyful Wisdom, Human, All Too Human</t>
+          <t>Thus Spake Zarathustra, Beyond Good and Evil, become who you are, God is dead, The Joyful Wisdom, Human, All Too Human</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>active love, self-deception, The Brothers Karamazov, Notes from Underground</t>
+          <t>The Brothers Karamazov, Notes from Underground, Crime and Punishment, active love, self-deception</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5978,7 +5978,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>daimon</t>
+          <t>fragments, everything flows, daimon, Logos</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr"/>
@@ -6203,7 +6203,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>moral law, good will, respect, Groundwork, Critique of Practical Reason</t>
+          <t>Groundwork, Critique of Practical Reason, categorical imperative, moral law, good will, respect</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Mill's Autobiography, On Liberty</t>
+          <t>On Liberty, Utilitarianism, The Subjection of Women, Mill's Autobiography, harm principle</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -7103,7 +7103,7 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>maxim</t>
+          <t>Maxims, self-love, moralists, maxim</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Lao Tzŭ, Laotse, Tao Te Ching</t>
+          <t>Tao Te Ching, wu wei, the Way</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Lao Tzu</t>
+          <t>Lao Tzu, Lao Tzŭ, Laotse</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr"/>
@@ -7890,7 +7890,7 @@
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Mengzi, human nature</t>
+          <t>human nature, righteousness, the people first</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -8567,7 +8567,7 @@
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Laws, Apology, Socratic wisdom, Socrates, Crito, Phaedo, Republic, Symposium, Phaedrus, Gorgias, Theaetetus, Meno</t>
+          <t>Republic, Apology, Symposium, Phaedo, Socrates, Socratic wisdom, Laws, Crito, Phaedrus, Gorgias, Theaetetus, Meno</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr"/>
@@ -8785,7 +8785,7 @@
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>self-reliance, Nature</t>
+          <t>Self-Reliance, Nature, Transcendentalism</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -9458,7 +9458,7 @@
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>attention</t>
+          <t>The Need for Roots, attention, Gravity and Grace, factory work</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -9681,7 +9681,7 @@
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>non-attachment</t>
+          <t>Krishna, Arjuna, non-attachment, karma yoga, svadharma</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -9792,7 +9792,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>the wise</t>
+          <t>the Buddha, the wise, Dhamma</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -9904,7 +9904,7 @@
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Nagasena</t>
+          <t>Nagasena, Menander, the chariot</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -10021,7 +10021,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Katha Upanishad, Isha Upanishad, Brihadaranyaka Upanishad, Mundaka Upanishad</t>
+          <t>Atman, Brahman, Katha Upanishad, Isha Upanishad, Brihadaranyaka Upanishad, Mundaka Upanishad</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -10132,7 +10132,7 @@
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>commonwealth, Leviathan</t>
+          <t>Leviathan, commonwealth, social contract, state of nature</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -10356,7 +10356,7 @@
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>citizen of the world, Candide, Zadig, Philosophical Dictionary</t>
+          <t>Candide, Philosophical Dictionary, Zadig, citizen of the world, tolerance</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr"/>
@@ -10572,12 +10572,12 @@
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>great knowledge, the useless tree, Chuang Tzŭ</t>
+          <t>the useless tree, great knowledge, butterfly dream</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Chuang Tzu</t>
+          <t>Chuang Tzu, Chuang Tzŭ</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr"/>
@@ -10685,7 +10685,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Discourse on Happiness</t>
+          <t>Discourse on Happiness, Newton's Principia, physics</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -10793,7 +10793,7 @@
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>beauty, art, aesthetics, taste</t>
+          <t>aesthetics, taste, wabi-sabi, imperfection, the beautiful</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr"/>
@@ -10889,7 +10889,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>change, impermanence, transience, flux</t>
+          <t>transience, flux, mono no aware, everything passes</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr"/>
@@ -10984,7 +10984,7 @@
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>character, virtue, integrity, junzi, gentleman</t>
+          <t>integrity, junzi, superior man, moral character, honesty</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr"/>
@@ -11081,7 +11081,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>death, mortality, dying, grief, memento mori</t>
+          <t>dying, grief, memento mori, afterlife, fear of death</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr"/>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>democracy, voting, citizens, government</t>
+          <t>voting, the people, citizens, majority rule, self-government</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>craving, desire, simplicity, wanting less, possessions, contentment</t>
+          <t>craving, wanting less, contentment, non-attachment, possessions, frugality</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr"/>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>duty, moral law, good will, respect, categorical imperative, obligation</t>
+          <t>moral law, good will, categorical imperative, obligation, respect, svadharma</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr"/>
@@ -11471,7 +11471,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>ego, pride, humility, vanity, self-love</t>
+          <t>vanity, self-love, arrogance, modesty, self-conceit</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr"/>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>equality, inequality, fairness, women's rights</t>
+          <t>inequality, fairness, women's rights, natural rights, class</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr"/>
@@ -11667,7 +11667,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>fortune, luck, chance, fate, what is in our power, Fortuna</t>
+          <t>luck, fate, chance, Fortuna, what is in our power, wheel of fortune</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr"/>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>liberty, individuality, freedom, free will, choice, autonomy</t>
+          <t>liberty, free will, individuality, choice, autonomy, inner freedom</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr"/>
@@ -11869,7 +11869,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>friendship, friends, kindness, compassion</t>
+          <t>friends, compassion, generosity, benevolence, ren</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr"/>
@@ -11969,7 +11969,7 @@
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>habit, practice, discipline, routine</t>
+          <t>discipline, routine, training, repetition, self-discipline</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr"/>
@@ -12064,7 +12064,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>pleasure, happiness, the good life, eudaimonia, flourishing, wellbeing</t>
+          <t>pleasure, eudaimonia, flourishing, contentment, wellbeing, joy</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr"/>
@@ -12164,7 +12164,7 @@
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>social contract, justice, injustice, power, leadership</t>
+          <t>power, leadership, injustice, social contract, rulers, fairness</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>karma, dharma, dhamma, yoga, svadharma, rebirth</t>
+          <t>dhamma, svadharma, yoga, rebirth, intention</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr"/>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>law, rights, human rights, authority</t>
+          <t>human rights, natural rights, authority, rule of law, social contract</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr"/>
@@ -12457,7 +12457,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>learning, knowledge, education, wisdom, truth</t>
+          <t>education, wisdom, truth, ignorance, study, curiosity</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr"/>
@@ -12553,7 +12553,7 @@
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>love, romance, devotion, affection</t>
+          <t>romance, devotion, divine love, affection, longing</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr"/>
@@ -12649,7 +12649,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>reason, passions, judgment, hatred, emotions, feelings, mind, anger</t>
+          <t>passions, reason, judgment, anger, feelings, hatred</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr"/>
@@ -12745,7 +12745,7 @@
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>nature, universe, cosmos, the natural world</t>
+          <t>cosmos, the natural world, atoms, Tao, seasons</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr"/>
@@ -12841,7 +12841,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>purpose, meaning, calling, meaning of life</t>
+          <t>meaning of life, calling, vocation, why live, nihilism</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr"/>
@@ -12936,7 +12936,7 @@
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>self-knowledge, know thyself, introspection, self-examination</t>
+          <t>know thyself, introspection, self-examination, the unexamined life, masks</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr"/>
@@ -13032,7 +13032,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>solitude, stillness, silence, being alone</t>
+          <t>silence, being alone, retreat, quiet, hermit</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr"/>
@@ -13127,7 +13127,7 @@
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>suffering, resilience, pain, adversity, hardship</t>
+          <t>pain, adversity, hardship, consolation, grief</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr"/>
@@ -13222,7 +13222,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>self, soul, Atman, Brahman, not-self, nafs, the lower self</t>
+          <t>Atman, soul, not-self, nafs, Brahman, lower self</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr"/>
@@ -13320,7 +13320,7 @@
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>time, the present moment, now, past and future</t>
+          <t>present moment, carpe diem, past and future, memory, the moment</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr"/>
@@ -13419,7 +13419,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>prejudice, tolerance, intolerance, diversity, religious freedom</t>
+          <t>prejudice, intolerance, diversity, religious freedom, toleration</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr"/>
@@ -13520,7 +13520,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>war, peace, violence, conflict</t>
+          <t>violence, conflict, nonviolence, revenge</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr"/>
@@ -13617,7 +13617,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>work, action, effort, doing</t>
+          <t>effort, doing, karma yoga, wu wei, labour</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr"/>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>wealth, money, poverty, riches, work</t>
+          <t>money, poverty, riches, labour, possessions</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr"/>

--- a/content/pages.xlsx
+++ b/content/pages.xlsx
@@ -828,7 +828,7 @@
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO2" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO3" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO4" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO5" s="2" t="inlineStr">
@@ -1293,12 +1293,12 @@
 - [Brihadaranyaka Upanishad](https://en.wikipedia.org/wiki/Brihadaranyaka_Upanishad) (Wikipedia)
 - [Bhagavad Gita](https://en.wikipedia.org/wiki/Bhagavad_Gita) (Wikipedia)
 - [Milinda Panha](https://en.wikipedia.org/wiki/Milinda_Panha) (Wikipedia)
-- [Bhagavadgita](https://www.britannica.com/topic/Bhagavadgita) (Encyclopædia Britannica)</t>
+- [Bhagavad Gita](https://www.britannica.com/topic/Bhagavad-Gita) (Encyclopædia Britannica)</t>
         </is>
       </c>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO6" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO7" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO8" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO9" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO10" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO11" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO12" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO13" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO14" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AN15" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO15" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO16" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AN17" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO17" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AN18" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO18" s="2" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AN19" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO19" s="2" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO20" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AN21" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO21" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO22" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AN23" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO23" s="2" t="inlineStr">
@@ -3343,7 +3343,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>Sei Shōnagon, Kamo no Chōmei, Kenkō, and Kakuzo Okakura.</t>
+          <t>Sei Shōnagon, Kamo no Chōmei, Kenkō, and Okakura Kakuzō.</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="AN24" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO24" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AN25" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO25" s="2" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO26" s="2" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="AN27" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO27" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO28" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="AN29" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO29" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AN30" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO30" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>**Arthur Schopenhauer** · Danzig, Poland · 1788 – 1860 · Existential Thought</t>
+          <t>**Arthur Schopenhauer** · Danzig (now Gdańsk, Poland) · 1788 – 1860 · Existential Thought</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="AN31" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO31" s="2" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="AN32" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO32" s="2" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO33" s="2" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO34" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="AN35" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO35" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="AN36" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO36" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="AN37" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="AN38" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO38" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AN39" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO39" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO40" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="AN41" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO41" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="AN42" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO42" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="AN43" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO43" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="AN44" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AN45" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO45" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AN46" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO46" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AN47" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO47" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="AN48" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO48" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="AN49" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO49" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>**Immanuel Kant** · Königsberg, Russia · 1724 – 1804 · Enlightenment Ethics</t>
+          <t>**Immanuel Kant** · Königsberg (now Kaliningrad, Russia) · 1724 – 1804 · Enlightenment Ethics</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AN50" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO50" s="2" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="AN51" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO51" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="AN52" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO52" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AN53" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO53" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AN54" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO54" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>thinker-kakuzo-okakura</t>
+          <t>thinker-kamo-no-chomei</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Kakuzo Okakura</t>
+          <t>Kamo no Chōmei</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>**Kakuzo Okakura** · Yokohama, Japan · 1863 – 1913 · Japanese Aesthetics</t>
+          <t>**Kamo no Chōmei** · Japan · about 1155 – 1216 · Japanese Aesthetics</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Asia meets the West</t>
+          <t>Japan, from the Heian court to the age of the samurai</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
@@ -6771,20 +6771,20 @@
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>The Book of Tea</t>
+          <t>Hōjōki</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Okakura Kakuzō, Okakura Tenshin, Okakura</t>
+          <t>Chōmei</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Okakura grew up in Yokohama, studying Western culture at school and Japanese tradition in a Buddhist temple. At the Tokyo Imperial University he studied with the American art historian Ernest Fenollosa, and he went on to work for the Ministry of Education.
-In 1887 he helped found the Tokyo School of Fine Arts, and he soon became its director. When it began to favour European methods, he resigned and started a new academy with leading artists, to learn from Western art without losing Japanese inspiration. From 1906 he worked at the Museum of Fine Arts in Boston, where he became curator of Japanese and Chinese art.</t>
+          <t>Chōmei was the second son of the head priest of the Lower Kamo Shinto shrine in Kyoto. He grew up at court, loved music, and was known as a fine player of the *biwa*, a Japanese lute. In his thirties his poems won contests and appeared in anthologies, and the retired emperor Go-Toba appointed him to his Imperial Poetry Office.
+But he lost his political backing and was passed over for the post at his family's shrine; a cousin got it instead. In 1204 he turned his back on society, took Buddhist vows, and became a hermit. After a few years at the foot of Mount Hiei, he built a tiny hut in the hills of Hino, south-east of the capital, and lived there for the rest of his life.</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr"/>
@@ -6793,12 +6793,11 @@
       <c r="S55" s="2" t="inlineStr"/>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>He wrote his main works in English, to speak directly to Western readers. In *The Book of Tea* (1906), tea becomes a way of seeing life:
-- **The beauty of the imperfect:** true beauty is found by one who completes the incomplete in the mind.
-- **Emptiness is useful:** a pitcher's value lies in the space where water goes.
-- **Leave something unsaid,** so others can finish the thought.
-- **Small things reveal us:** the art of life lies in everyday details.
-- **East and West can complete each other,** if each learns to respect the other.</t>
+          <t>In the hut he wrote *Hōjōki*, *An Account of a Ten-Foot-Square Hut* (1212). It opens with a river that never stops flowing and is never the same water. His themes:
+- **Impermanence:** people and houses are like foam on the water, here and gone.
+- **Disaster:** fires, a whirlwind, famine, and an earthquake that struck Kyoto in his lifetime.
+- **Owning less:** a small, movable hut is enough, and frees you from worry.
+- **Solitude:** music, poems, and walks in the hills as company.</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr"/>
@@ -6810,14 +6809,14 @@
       <c r="AA55" s="2" t="inlineStr"/>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>*The Book of Tea* was partly a reply. Written just after the Russo-Japanese War, it protested Western caricatures of Japan, and the fear that Japan was respected only once it adopted the West's taste for war.
-He also spent two years in India and talked with Vivekananda and Tagore, two other voices in the app. In Boston, he once hosted a tea ceremony by candlelight for the art collector Isabella Stewart Gardner.</t>
+          <t>He was an unusual hermit for his time. Most people who left the world joined a monastery; Chōmei lived alone instead.
+He is also more human than his serene book suggests. He still held a grudge against the cousin who took the shrine post. And though he writes in *Hōjōki* that he never left his hut, another account says he made at least one journey away from it.</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>*The Book of Tea*, chapter I. Short, warm, and written in English. Free on Project Gutenberg.</t>
+          <t>*Hōjōki*: only a few dozen pages. W. G. Aston's 1899 translation, in *A History of Japanese Literature*, is free online.</t>
         </is>
       </c>
       <c r="AE55" s="2" t="inlineStr"/>
@@ -6830,18 +6829,19 @@
       <c r="AL55" s="2" t="inlineStr"/>
       <c r="AM55" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Okakura Kakuzō": https://en.wikipedia.org/wiki/Okakura_Kakuz%C5%8D
-- The app's Okakura thoughts (#528–537, #550–554), from *The Book of Tea*</t>
+          <t>- Wikipedia, "Kamo no Chōmei": https://en.wikipedia.org/wiki/Kamo_no_Ch%C5%8Dmei
+- Wikipedia, "Hōjōki": https://en.wikipedia.org/wiki/H%C5%8Dj%C5%8Dki
+- The app's Chōmei thoughts (#538–541), from *Hōjōki*</t>
         </is>
       </c>
       <c r="AN55" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO55" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages batch 4</t>
+          <t>Thinker pages batch 5</t>
         </is>
       </c>
       <c r="AP55" s="2" t="inlineStr"/>
@@ -6849,7 +6849,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>thinker-kamo-no-chomei</t>
+          <t>thinker-kenko</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Kamo no Chōmei</t>
+          <t>Kenkō</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>**Kamo no Chōmei** · Japan · about 1155 – 1216 · Japanese Aesthetics</t>
+          <t>**Kenkō** · Japan · about 1283 – 1350 · Japanese Aesthetics</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6883,20 +6883,16 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Hōjōki</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>Chōmei</t>
-        </is>
-      </c>
+          <t>Essays in Idleness</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Chōmei was the second son of the head priest of the Lower Kamo Shinto shrine in Kyoto. He grew up at court, loved music, and was known as a fine player of the *biwa*, a Japanese lute. In his thirties his poems won contests and appeared in anthologies, and the retired emperor Go-Toba appointed him to his Imperial Poetry Office.
-But he lost his political backing and was passed over for the post at his family's shrine; a cousin got it instead. In 1204 he turned his back on society, took Buddhist vows, and became a hermit. After a few years at the foot of Mount Hiei, he built a tiny hut in the hills of Hino, south-east of the capital, and lived there for the rest of his life.</t>
+          <t>Kenkō was the son of an official and served as an officer of the guards at the imperial palace in Kyoto. Later in life he left public life and became a Buddhist monk and hermit.
+Nobody knows why. One story says it was an unhappy love; another, grief at the death of a former emperor. He kept writing poetry and took part in poetry contests at court, but his fame rests on one book, written between 1330 and 1332.</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr"/>
@@ -6905,11 +6901,11 @@
       <c r="S56" s="2" t="inlineStr"/>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>In the hut he wrote *Hōjōki*, *An Account of a Ten-Foot-Square Hut* (1212). It opens with a river that never stops flowing and is never the same water. His themes:
-- **Impermanence:** people and houses are like foam on the water, here and gone.
-- **Disaster:** fires, a whirlwind, famine, and an earthquake that struck Kyoto in his lifetime.
-- **Owning less:** a small, movable hut is enough, and frees you from worry.
-- **Solitude:** music, poems, and walks in the hills as company.</t>
+          <t>*Essays in Idleness* is a collection of 243 short pieces, from a single line to a few pages. He wrote in a "follow the brush" style, letting one thought lead to the next. His main themes:
+- **Impermanence:** everything passes, and that is part of its beauty.
+- **Death:** it comes sooner than we think, so do not waste your days.
+- **Nature and small things:** flowers before they bloom, a garden strewn with fallen ones, the moon as it wanes.
+- **People:** friendship, manners, and the follies of those around him.</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr"/>
@@ -6921,14 +6917,14 @@
       <c r="AA56" s="2" t="inlineStr"/>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>He was an unusual hermit for his time. Most people who left the world joined a monastery; Chōmei lived alone instead.
-He is also more human than his serene book suggests. He still held a grudge against the cousin who took the shrine post. And though he writes in *Hōjōki* that he never left his hut, another account says he made at least one journey away from it.</t>
+          <t>For a monk writing about death, Kenkō is often funny. He tells little stories from everyday life, like the archery teacher who tells a beginner to carry only one arrow, and he has firm views on taste: a little imperfection, he says, beats perfect sameness.
+The book was not published in his lifetime and was not even divided into numbered passages until the 17th century. Even his name has a twist: "Yoshida Kenkō" comes from later documents that recent research has shown to be forged.</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>*Hōjōki*: only a few dozen pages. W. G. Aston's 1899 translation, in *A History of Japanese Literature*, is free online.</t>
+          <t>*Essays in Idleness*: open it anywhere and read one passage at a time. William N. Porter's 1914 translation, *A Miscellany of a Japanese Priest*, is free on archive.org.</t>
         </is>
       </c>
       <c r="AE56" s="2" t="inlineStr"/>
@@ -6941,19 +6937,19 @@
       <c r="AL56" s="2" t="inlineStr"/>
       <c r="AM56" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Kamo no Chōmei": https://en.wikipedia.org/wiki/Kamo_no_Ch%C5%8Dmei
-- Wikipedia, "Hōjōki": https://en.wikipedia.org/wiki/H%C5%8Dj%C5%8Dki
-- The app's Chōmei thoughts (#538–541), from *Hōjōki*</t>
+          <t>- Wikipedia, "Yoshida Kenkō": https://en.wikipedia.org/wiki/Yoshida_Kenk%C5%8D
+- Wikipedia, "Tsurezuregusa": https://en.wikipedia.org/wiki/Tsurezuregusa
+- The app's Kenkō thoughts (#515–527, #546–547) and their translations</t>
         </is>
       </c>
       <c r="AN56" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO56" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages batch 5</t>
+          <t>Thinker pages batch 2</t>
         </is>
       </c>
       <c r="AP56" s="2" t="inlineStr"/>
@@ -6961,7 +6957,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>thinker-kenko</t>
+          <t>thinker-la-rochefoucauld</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -6971,22 +6967,22 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Kenkō</t>
+          <t>La Rochefoucauld</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>**Kenkō** · Japan · about 1283 – 1350 · Japanese Aesthetics</t>
+          <t>**François de La Rochefoucauld** · Paris, France · 1613 – 1680 · Humanists and Essayists</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Japanese Aesthetics</t>
+          <t>Humanists and Essayists</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Japan, from the Heian court to the age of the samurai</t>
+          <t>Europe in the 17th century</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -6995,16 +6991,20 @@
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Essays in Idleness</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr"/>
+          <t>Maxims, self-love, moralists, maxim</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>François de La Rochefoucauld</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Kenkō was the son of an official and served as an officer of the guards at the imperial palace in Kyoto. Later in life he left public life and became a Buddhist monk and hermit.
-Nobody knows why. One story says it was an unhappy love; another, grief at the death of a former emperor. He kept writing poetry and took part in poetry contests at court, but his fame rests on one book, written between 1330 and 1332.</t>
+          <t>La Rochefoucauld was born in Paris into one of the greatest noble families of France. He was married at fourteen and commanding a regiment at sixteen. As a young courtier he plotted against the powerful Cardinal Richelieu, which earned him eight days in the Bastille and spells of exile from court.
+In the 1640s and 1650s he joined the Fronde, a rebellion of nobles against the crown, and was badly wounded in the fighting. After that he withdrew from politics, wrote his memoirs, and became a regular of the Paris literary salons.</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr"/>
@@ -7013,11 +7013,11 @@
       <c r="S57" s="2" t="inlineStr"/>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>*Essays in Idleness* is a collection of 243 short pieces, from a single line to a few pages. He wrote in a "follow the brush" style, letting one thought lead to the next. His main themes:
-- **Impermanence:** everything passes, and that is part of its beauty.
-- **Death:** it comes sooner than we think, so do not waste your days.
-- **Nature and small things:** flowers before they bloom, a garden strewn with fallen ones, the moon as it wanes.
-- **People:** friendship, manners, and the follies of those around him.</t>
+          <t>In 1665 he published, anonymously, his *Maxims*: in the end 504 short sayings, most just two or three lines. They look hard at why people really act:
+- **Self-love:** much of what we call virtue is self-interest in disguise.
+- **Disguise:** we hide from others for so long that in the end we hide from ourselves.
+- **Love and friendship** are rarely as pure as we claim.
+- **Hypocrisy:** even false virtue is a tribute, since hypocrisy is the homage vice pays to virtue.</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr"/>
@@ -7029,14 +7029,14 @@
       <c r="AA57" s="2" t="inlineStr"/>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>For a monk writing about death, Kenkō is often funny. He tells little stories from everyday life, like the archery teacher who tells a beginner to carry only one arrow, and he has firm views on taste: a little imperfection, he says, beats perfect sameness.
-The book was not published in his lifetime and was not even divided into numbered passages until the 17th century. Even his name has a twist: "Yoshida Kenkō" comes from later documents that recent research has shown to be forged.</t>
+          <t>Many readers find the *Maxims* cynical, even bitter. Yet they grew out of a social game. In the salon of the Marquise de Sablé, guests polished short sayings together, and La Rochefoucauld kept revising his for the rest of his life.
+He also tried to escape his own reputation: when a version of his memoirs appeared without his consent, he denied it was genuine, but few people believed him.</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>*Essays in Idleness*: open it anywhere and read one passage at a time. William N. Porter's 1914 translation, *A Miscellany of a Japanese Priest*, is free on archive.org.</t>
+          <t>The *Maxims*: open them anywhere and read three or four at a time. The 1871 translation by J. W. Willis Bund and J. Hain Friswell is free on Project Gutenberg.</t>
         </is>
       </c>
       <c r="AE57" s="2" t="inlineStr"/>
@@ -7049,19 +7049,19 @@
       <c r="AL57" s="2" t="inlineStr"/>
       <c r="AM57" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Yoshida Kenkō": https://en.wikipedia.org/wiki/Yoshida_Kenk%C5%8D
-- Wikipedia, "Tsurezuregusa": https://en.wikipedia.org/wiki/Tsurezuregusa
-- The app's Kenkō thoughts (#515–527, #546–547) and their translations</t>
+          <t>- Wikipedia, "François de La Rochefoucauld (writer)": https://en.wikipedia.org/wiki/Fran%C3%A7ois_de_La_Rochefoucauld_(writer)
+- Wikipedia, "French moralists": https://en.wikipedia.org/wiki/French_moralists
+- The app's La Rochefoucauld thoughts (#271–275, #286, #299–302), from the *Maxims*</t>
         </is>
       </c>
       <c r="AN57" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO57" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages batch 2</t>
+          <t>Thinker pages batch 3</t>
         </is>
       </c>
       <c r="AP57" s="2" t="inlineStr"/>
@@ -7069,7 +7069,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>thinker-la-rochefoucauld</t>
+          <t>thinker-laozi</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7079,22 +7079,22 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>La Rochefoucauld</t>
+          <t>Laozi</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>**François de La Rochefoucauld** · Paris, France · 1613 – 1680 · Humanists and Essayists</t>
+          <t>**Laozi** · China · traditionally 6th century BCE · Taoism</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Humanists and Essayists</t>
+          <t>Taoism</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Europe in the 17th century</t>
+          <t>China of the Hundred Schools</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -7103,20 +7103,20 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Maxims, self-love, moralists, maxim</t>
+          <t>Tao Te Ching, wu wei, the Way</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>François de La Rochefoucauld</t>
+          <t>Lao Tzu, Lao Tzŭ, Laotse</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>La Rochefoucauld was born in Paris into one of the greatest noble families of France. He was married at fourteen and commanding a regiment at sixteen. As a young courtier he plotted against the powerful Cardinal Richelieu, which earned him eight days in the Bastille and spells of exile from court.
-In the 1640s and 1650s he joined the Fronde, a rebellion of nobles against the crown, and was badly wounded in the fighting. After that he withdrew from politics, wrote his memoirs, and became a regular of the Paris literary salons.</t>
+          <t>We are not sure. The earliest accounts say Laozi, "the Old Master", was a man called Li Er or Lao Dan, who kept the archives at the Zhou court and was an older contemporary of Confucius. Scholars are divided: some accept that a Lao Dan probably lived, others see him as largely or wholly a legend.
+The best-known story says that, at the age of 80, he set off west to live as a hermit. At the last gate, a guard named Yinxi recognised him and asked him to write down his wisdom before leaving. What he wrote, the story goes, was the *Tao Te Ching*.</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr"/>
@@ -7125,11 +7125,11 @@
       <c r="S58" s="2" t="inlineStr"/>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>In 1665 he published, anonymously, his *Maxims*: in the end 504 short sayings, most just two or three lines. They look hard at why people really act:
-- **Self-love:** much of what we call virtue is self-interest in disguise.
-- **Disguise:** we hide from others for so long that in the end we hide from ourselves.
-- **Love and friendship** are rarely as pure as we claim.
-- **Hypocrisy:** even false virtue is a tribute, since hypocrisy is the homage vice pays to virtue.</t>
+          <t>- **The Tao:** the way of all things, which cannot be fully named.
+- **Effortless action:** the wise act without forcing, and things get done.
+- **Water as a model:** soft and low, it serves everything and wears down the hardest stone.
+- **Less is more:** fewer desires, fewer possessions, fewer rules.
+- **Quiet leadership:** the best rulers are barely noticed.</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr"/>
@@ -7141,14 +7141,14 @@
       <c r="AA58" s="2" t="inlineStr"/>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>Many readers find the *Maxims* cynical, even bitter. Yet they grew out of a social game. In the salon of the Marquise de Sablé, guests polished short sayings together, and La Rochefoucauld kept revising his for the rest of his life.
-He also tried to escape his own reputation: when a version of his memoirs appeared without his consent, he denied it was genuine, but few people believed him.</t>
+          <t>The oldest pieces of the *Tao Te Ching* ever found were written on bamboo strips buried around 300 BCE. They hold only about 40 percent of the text we read today, which suggests the book grew over time.
+Later, Laozi became far more than a writer. From the Han dynasty on, religious Taoism worshipped him as a god, and the Tang emperors claimed him as their ancestor.</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>The *Maxims*: open them anywhere and read three or four at a time. The 1871 translation by J. W. Willis Bund and J. Hain Friswell is free on Project Gutenberg.</t>
+          <t>The *Tao Te Ching*: 81 short chapters, best read one at a time. James Legge's 1891 translation is free on Project Gutenberg.</t>
         </is>
       </c>
       <c r="AE58" s="2" t="inlineStr"/>
@@ -7161,19 +7161,19 @@
       <c r="AL58" s="2" t="inlineStr"/>
       <c r="AM58" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "François de La Rochefoucauld (writer)": https://en.wikipedia.org/wiki/Fran%C3%A7ois_de_La_Rochefoucauld_(writer)
-- Wikipedia, "French moralists": https://en.wikipedia.org/wiki/French_moralists
-- The app's La Rochefoucauld thoughts (#271–275, #286, #299–302), from the *Maxims*</t>
+          <t>- Wikipedia, "Laozi": https://en.wikipedia.org/wiki/Laozi
+- Wikipedia, "Tao Te Ching": https://en.wikipedia.org/wiki/Tao_Te_Ching
+- The app's Laozi thoughts (#410–428, #441–451), including #410, #422, and #442</t>
         </is>
       </c>
       <c r="AN58" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO58" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages batch 3</t>
+          <t>Thinker pages batch 2</t>
         </is>
       </c>
       <c r="AP58" s="2" t="inlineStr"/>
@@ -7181,7 +7181,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>thinker-laozi</t>
+          <t>thinker-leo-tolstoy</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -7191,22 +7191,22 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Laozi</t>
+          <t>Leo Tolstoy</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>**Laozi** · China · traditionally 6th century BCE · Taoism</t>
+          <t>**Leo Tolstoy** · Yasnaya Polyana, Russia · 1828 – 1910 · Existential Thought</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Taoism</t>
+          <t>Existential Thought</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>China of the Hundred Schools</t>
+          <t>Europe and Russia in the 19th century</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -7215,20 +7215,21 @@
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Tao Te Ching, wu wei, the Way</t>
+          <t>A Confession</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Lao Tzu, Lao Tzŭ, Laotse</t>
+          <t>Tolstoy</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>We are not sure. The earliest accounts say Laozi, "the Old Master", was a man called Li Er or Lao Dan, who kept the archives at the Zhou court and was an older contemporary of Confucius. Scholars are divided: some accept that a Lao Dan probably lived, others see him as largely or wholly a legend.
-The best-known story says that, at the age of 80, he set off west to live as a hermit. At the last gate, a guard named Yinxi recognised him and asked him to write down his wisdom before leaving. What he wrote, the story goes, was the *Tao Te Ching*.</t>
+          <t>Tolstoy was born in 1828 into a family of Russian counts, on the estate of Yasnaya Polyana south of Moscow. His mother died when he was two and his father when he was nine. He left university without a degree, ran up gambling debts, and joined the army, serving as an artillery officer in the siege of Sevastopol.
+In 1862 he married Sophia Behrs, and they had 13 children, eight of whom survived childhood. In the years that followed he wrote *War and Peace* (1869) and *Anna Karenina* (1878), often named among the greatest novels ever written.
+Then, in his early fifties, came a crisis of meaning, and a turn to a radical, personal Christianity. He gave up meat and tried to give up his wealth. In 1910, aged 82, he set off on a train journey and died of pneumonia at a small railway station.</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr"/>
@@ -7237,11 +7238,12 @@
       <c r="S59" s="2" t="inlineStr"/>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>- **The Tao:** the way of all things, which cannot be fully named.
-- **Effortless action:** the wise act without forcing, and things get done.
-- **Water as a model:** soft and low, it serves everything and wears down the hardest stone.
-- **Less is more:** fewer desires, fewer possessions, fewer rules.
-- **Quiet leadership:** the best rulers are barely noticed.</t>
+          <t>*A Confession* (written 1879–1880) tells how success stopped meaning anything to him, and how he searched for a reason to live. His themes:
+- **The question of meaning:** if death is certain, what is the point of what I do today?
+- **Success is not an answer:** fame, family, and wealth did not save him from despair.
+- **Honesty about despair:** he describes the crisis plainly, without dressing it up.
+- **Faith as a way of living:** he came to read the Sermon on the Mount literally, as rules for life.
+- **Non-violence:** never resist evil by force, a view that later shaped Gandhi and Martin Luther King Jr.</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr"/>
@@ -7253,14 +7255,14 @@
       <c r="AA59" s="2" t="inlineStr"/>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>The oldest pieces of the *Tao Te Ching* ever found were written on bamboo strips buried around 300 BCE. They hold only about 40 percent of the text we read today, which suggests the book grew over time.
-Later, Laozi became far more than a writer. From the Han dynasty on, religious Taoism worshipped him as a god, and the Tang emperors claimed him as their ancestor.</t>
+          <t>The author of *War and Peace* came to reject his own great novels, along with most of modern Western culture. His ideas also led the Russian Orthodox Church to excommunicate him in 1901, and the Church's censors cut *A Confession* from the journal that first tried to print it.
+His home life suffered as his views hardened. His wish to give away his wealth and the copyrights to his books caused deep conflict with his wife. He was nominated for the Nobel Prize several times and never won it.</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>The *Tao Te Ching*: 81 short chapters, best read one at a time. James Legge's 1891 translation is free on Project Gutenberg.</t>
+          <t>*A Confession*: short, direct, and personal. Aylmer Maude's English translation is free on Standard Ebooks.</t>
         </is>
       </c>
       <c r="AE59" s="2" t="inlineStr"/>
@@ -7273,19 +7275,20 @@
       <c r="AL59" s="2" t="inlineStr"/>
       <c r="AM59" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Laozi": https://en.wikipedia.org/wiki/Laozi
-- Wikipedia, "Tao Te Ching": https://en.wikipedia.org/wiki/Tao_Te_Ching
-- The app's Laozi thoughts (#410–428, #441–451), including #410, #422, and #442</t>
+          <t>- Encyclopædia Britannica, "Leo Tolstoy": https://www.britannica.com/biography/Leo-Tolstoy
+- Wikipedia, "Leo Tolstoy": https://en.wikipedia.org/wiki/Leo_Tolstoy
+- Wikipedia, "A Confession": https://en.wikipedia.org/wiki/A_Confession
+- The app's Tolstoy thoughts (#243–244), from *A Confession*, translated by Aylmer Maude</t>
         </is>
       </c>
       <c r="AN59" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO59" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages batch 2</t>
+          <t>Thinker pages, batch 6</t>
         </is>
       </c>
       <c r="AP59" s="2" t="inlineStr"/>
@@ -7293,7 +7296,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>thinker-leo-tolstoy</t>
+          <t>thinker-lucretius</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -7303,22 +7306,22 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Leo Tolstoy</t>
+          <t>Lucretius</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>**Leo Tolstoy** · Yasnaya Polyana, Russia · 1828 – 1910 · Existential Thought</t>
+          <t>**Lucretius** · Italy · about 99 – 55 BCE · Epicureanism</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Existential Thought</t>
+          <t>Epicureanism</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Europe and Russia in the 19th century</t>
+          <t>Rome, from the Republic to its fall</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -7327,21 +7330,16 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>A Confession</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>Tolstoy</t>
-        </is>
-      </c>
+          <t>On the Nature of Things</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Tolstoy was born in 1828 into a family of Russian counts, on the estate of Yasnaya Polyana south of Moscow. His mother died when he was two and his father when he was nine. He left university without a degree, ran up gambling debts, and joined the army, serving as an artillery officer in the siege of Sevastopol.
-In 1862 he married Sophia Behrs, and they had 13 children, eight of whom survived childhood. In the years that followed he wrote *War and Peace* (1869) and *Anna Karenina* (1878), often named among the greatest novels ever written.
-Then, in his early fifties, came a crisis of meaning, and a turn to a radical, personal Christianity. He gave up meat and tried to give up his wealth. In 1910, aged 82, he set off on a train journey and died of pneumonia at a small railway station.</t>
+          <t>We know almost nothing about Lucretius's life. The only sure fact is that he was a friend, or a client, of a Roman politician named Gaius Memmius, to whom he dedicated his one surviving work. He lived in the last, violent years of the Roman Republic, in the age of Cicero.
+That work is *On the Nature of Things*, a long poem in Latin that sets out the philosophy of Epicurus. It shaped the great Roman poets who came after him, above all Virgil.</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr"/>
@@ -7350,12 +7348,12 @@
       <c r="S60" s="2" t="inlineStr"/>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>*A Confession* (written 1879–1880) tells how success stopped meaning anything to him, and how he searched for a reason to live. His themes:
-- **The question of meaning:** if death is certain, what is the point of what I do today?
-- **Success is not an answer:** fame, family, and wealth did not save him from despair.
-- **Honesty about despair:** he describes the crisis plainly, without dressing it up.
-- **Faith as a way of living:** he came to read the Sermon on the Mount literally, as rules for life.
-- **Non-violence:** never resist evil by force, a view that later shaped Gandhi and Martin Luther King Jr.</t>
+          <t>Lucretius used poetry to carry Epicurus's ideas to Roman readers. His aim was to free them from fear:
+- **Nothing comes from nothing,** and nothing ever returns to nothing.
+- **The world is made of tiny particles** moving in empty space, always coming together and falling apart.
+- **Fear comes from ignorance:** people blame the gods for what they do not understand.
+- **Death is no evil:** leave life like a guest who has eaten well at a banquet.
+- **Everything changes:** nations rise and fall, and drops of water wear away stone.</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr"/>
@@ -7367,14 +7365,14 @@
       <c r="AA60" s="2" t="inlineStr"/>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>The author of *War and Peace* came to reject his own great novels, along with most of modern Western culture. His ideas also led the Russian Orthodox Church to excommunicate him in 1901, and the Church's censors cut *A Confession* from the journal that first tried to print it.
-His home life suffered as his views hardened. His wish to give away his wealth and the copyrights to his books caused deep conflict with his wife. He was nominated for the Nobel Prize several times and never won it.</t>
+          <t>The poem was almost lost. It survived the Middle Ages in very few copies until an Italian book hunter, Poggio Bracciolini, found one in a German monastery in 1417. It then fed the revival of atomism in early modern science, and Montaigne owned and annotated a copy.
+A strange legend, recorded by Saint Jerome four centuries later, says Lucretius was driven mad by a love potion and took his own life. Scholars doubt it, not least because the same ancient notes get other basic facts about him wrong.</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>*A Confession*: short, direct, and personal. Aylmer Maude's English translation is free on Standard Ebooks.</t>
+          <t>*On the Nature of Things*, Book I, especially the opening sections on atoms and fear. William Ellery Leonard's 1916 verse translation is free on Project Gutenberg.</t>
         </is>
       </c>
       <c r="AE60" s="2" t="inlineStr"/>
@@ -7387,20 +7385,18 @@
       <c r="AL60" s="2" t="inlineStr"/>
       <c r="AM60" s="2" t="inlineStr">
         <is>
-          <t>- Encyclopædia Britannica, "Leo Tolstoy": https://www.britannica.com/biography/Leo-Tolstoy
-- Wikipedia, "Leo Tolstoy": https://en.wikipedia.org/wiki/Leo_Tolstoy
-- Wikipedia, "A Confession": https://en.wikipedia.org/wiki/A_Confession
-- The app's Tolstoy thoughts (#243–244), from *A Confession*, translated by Aylmer Maude</t>
+          <t>- Wikipedia, "Lucretius": https://en.wikipedia.org/wiki/Lucretius
+- The app's Lucretius thoughts (#74–76, #87–94), from *On the Nature of Things*</t>
         </is>
       </c>
       <c r="AN60" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO60" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages, batch 6</t>
+          <t>Thinker pages batch 5</t>
         </is>
       </c>
       <c r="AP60" s="2" t="inlineStr"/>
@@ -7408,7 +7404,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>thinker-lucretius</t>
+          <t>thinker-marcus-aurelius</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -7418,17 +7414,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Lucretius</t>
+          <t>Marcus Aurelius</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>**Lucretius** · Italy · about 99 – 55 BCE · Epicureanism</t>
+          <t>**Marcus Aurelius** · Rome, Italy · 121 – 180 · Stoicism</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Epicureanism</t>
+          <t>Stoicism</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7442,16 +7438,20 @@
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>On the Nature of Things</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr"/>
+          <t>Meditations</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>We know almost nothing about Lucretius's life. The only sure fact is that he was a friend, or a client, of a Roman politician named Gaius Memmius, to whom he dedicated his one surviving work. He lived in the last, violent years of the Roman Republic, in the age of Cicero.
-That work is *On the Nature of Things*, a long poem in Latin that sets out the philosophy of Epicurus. It shaped the great Roman poets who came after him, above all Virgil.</t>
+          <t>Marcus lost his father at three and was raised by his mother and grandfather. In 138, the emperor Hadrian chose Antoninus Pius as his heir, and Antoninus in turn adopted Marcus. As heir to the throne, Marcus studied Greek and Latin with the best teachers of his time.
+He became emperor in 161 and ruled until his death in 180. It was a hard reign: wars in the East and along the Danube, and a plague that killed millions across the empire. He is remembered as the last of the "Five Good Emperors".</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr"/>
@@ -7460,12 +7460,11 @@
       <c r="S61" s="2" t="inlineStr"/>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>Lucretius used poetry to carry Epicurus's ideas to Roman readers. His aim was to free them from fear:
-- **Nothing comes from nothing,** and nothing ever returns to nothing.
-- **The world is made of tiny particles** moving in empty space, always coming together and falling apart.
-- **Fear comes from ignorance:** people blame the gods for what they do not understand.
-- **Death is no evil:** leave life like a guest who has eaten well at a banquet.
-- **Everything changes:** nations rise and fall, and drops of water wear away stone.</t>
+          <t>The *Meditations* are his private notes, written in Greek, many of them in army camps. He probably never meant them to be published. He keeps coming back to a few ideas:
+- **Do your duty** today, well, without waiting for thanks.
+- **We are made to work together,** like the hands and feet of one body.
+- **Your mind is yours:** things cannot disturb you, only your judgments about them.
+- **Everything passes,** including fame, so do not chase it.</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr"/>
@@ -7477,14 +7476,14 @@
       <c r="AA61" s="2" t="inlineStr"/>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>The poem was almost lost. It survived the Middle Ages in very few copies until an Italian book hunter, Poggio Bracciolini, found one in a German monastery in 1417. It then fed the revival of atomism in early modern science, and Montaigne owned and annotated a copy.
-A strange legend, recorded by Saint Jerome four centuries later, says Lucretius was driven mad by a love potion and took his own life. Scholars doubt it, not least because the same ancient notes get other basic facts about him wrong.</t>
+          <t>The most powerful man in the world filled his notes with reminders to be patient and humble. Yet his reign was far from peaceful, and he spent years at war.
+Persecution of Christians appears to have grown in his time, though historians think he was unlikely to have ordered it. He was also succeeded by his son, Commodus, and historians still debate that choice.</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>*On the Nature of Things*, Book I, especially the opening sections on atoms and fear. William Ellery Leonard's 1916 verse translation is free on Project Gutenberg.</t>
+          <t>*Meditations*, Book II: short and direct, and it opens with his famous advice for the start of each day. George Long's 1862 translation is free on Project Gutenberg.</t>
         </is>
       </c>
       <c r="AE61" s="2" t="inlineStr"/>
@@ -7497,18 +7496,19 @@
       <c r="AL61" s="2" t="inlineStr"/>
       <c r="AM61" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Lucretius": https://en.wikipedia.org/wiki/Lucretius
-- The app's Lucretius thoughts (#74–76, #87–94), from *On the Nature of Things*</t>
+          <t>- Wikipedia, "Marcus Aurelius": https://en.wikipedia.org/wiki/Marcus_Aurelius
+- Wikipedia, "Meditations": https://en.wikipedia.org/wiki/Meditations
+- The app's Marcus Aurelius thoughts (#1–14, #32–39), including #32 (Meditations 2.1)</t>
         </is>
       </c>
       <c r="AN61" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO61" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages batch 5</t>
+          <t>Thinker pages batch 2</t>
         </is>
       </c>
       <c r="AP61" s="2" t="inlineStr"/>
@@ -7516,7 +7516,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>thinker-marcus-aurelius</t>
+          <t>thinker-margaret-fuller</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7526,22 +7526,22 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Marcus Aurelius</t>
+          <t>Margaret Fuller</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>**Marcus Aurelius** · Rome, Italy · 121 – 180 · Stoicism</t>
+          <t>**Margaret Fuller** · Cambridge, United States · 1810 – 1850 · Humanists and Essayists</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Stoicism</t>
+          <t>Humanists and Essayists</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Rome, from the Republic to its fall</t>
+          <t>America in the 19th century</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -7550,36 +7550,36 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Meditations</t>
+          <t>Woman in the Nineteenth Century</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Fuller</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>Marcus lost his father at three and was raised by his mother and grandfather. In 138, the emperor Hadrian chose Antoninus Pius as his heir, and Antoninus in turn adopted Marcus. As heir to the throne, Marcus studied Greek and Latin with the best teachers of his time.
-He became emperor in 161 and ruled until his death in 180. It was a hard reign: wars in the East and along the Danube, and a plague that killed millions across the empire. He is remembered as the last of the "Five Good Emperors".</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>Fuller was born in Cambridgeport, Massachusetts. Her father, a lawyer, gave her an education as demanding as any boy's: she was translating Virgil from Latin as a small child. By her thirties she was known as the best-read person in New England, and she was the first woman allowed to use Harvard's library.
+From 1839 she ran "Conversations", discussion classes for women who had no access to higher education. Emerson made her the first editor of the Transcendentalist journal *The Dial*. In 1844 she joined the *New-York Tribune* as a critic, the first full-time book reviewer in American journalism.</t>
+        </is>
+      </c>
       <c r="Q62" s="2" t="inlineStr"/>
       <c r="R62" s="2" t="inlineStr"/>
       <c r="S62" s="2" t="inlineStr"/>
-      <c r="T62" s="2" t="inlineStr">
-        <is>
-          <t>The *Meditations* are his private notes, written in Greek, many of them in army camps. He probably never meant them to be published. He keeps coming back to a few ideas:
-- **Do your duty** today, well, without waiting for thanks.
-- **We are made to work together,** like the hands and feet of one body.
-- **Your mind is yours:** things cannot disturb you, only your judgments about them.
-- **Everything passes,** including fame, so do not chase it.</t>
-        </is>
-      </c>
-      <c r="U62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>Her book *Woman in the Nineteenth Century* (1845) is considered the first major feminist work in the United States. Its key points:
+- **Every path should be open to women** as freely as to men.
+- **Self-reliance is for everyone:** independence praised in men is called a fault in women.
+- **Growth:** people, women and men, are made to expand, not to be held in narrow roles.
+- **Education:** women deserve the same chance to learn and think as men.</t>
+        </is>
+      </c>
       <c r="V62" s="2" t="inlineStr"/>
       <c r="W62" s="2" t="inlineStr"/>
       <c r="X62" s="2" t="inlineStr"/>
@@ -7588,14 +7588,14 @@
       <c r="AA62" s="2" t="inlineStr"/>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>The most powerful man in the world filled his notes with reminders to be patient and humble. Yet his reign was far from peaceful, and he spent years at war.
-Persecution of Christians appears to have grown in his time, though historians think he was unlikely to have ordered it. He was also succeeded by his son, Commodus, and historians still debate that choice.</t>
+          <t>In 1846 the *Tribune* sent her to Europe as its first female foreign correspondent. In Italy she joined the side of the 1848 revolutions. During the siege of Rome she volunteered in hospitals, while her partner, Giovanni Ossoli, fought on the walls.
+In 1850 she sailed home with Ossoli and their child. The ship sank off Fire Island, near New York, and all three died; her body was never found. The leaders of the women's suffrage movement later wrote that she had more influence on American women's thinking than any woman before her.</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>*Meditations*, Book II: short and direct, and it opens with his famous advice for the start of each day. George Long's 1862 translation is free on Project Gutenberg.</t>
+          <t>*Woman in the Nineteenth Century*: bold and still fresh. Free on Project Gutenberg.</t>
         </is>
       </c>
       <c r="AE62" s="2" t="inlineStr"/>
@@ -7608,19 +7608,18 @@
       <c r="AL62" s="2" t="inlineStr"/>
       <c r="AM62" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Marcus Aurelius": https://en.wikipedia.org/wiki/Marcus_Aurelius
-- Wikipedia, "Meditations": https://en.wikipedia.org/wiki/Meditations
-- The app's Marcus Aurelius thoughts (#1–14, #32–39), including #32 (Meditations 2.1)</t>
+          <t>- Wikipedia, "Margaret Fuller": https://en.wikipedia.org/wiki/Margaret_Fuller
+- The app's Fuller thoughts (#293–295), from *Woman in the Nineteenth Century*</t>
         </is>
       </c>
       <c r="AN62" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO62" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages batch 2</t>
+          <t>Thinker pages batch 5</t>
         </is>
       </c>
       <c r="AP62" s="2" t="inlineStr"/>
@@ -7628,7 +7627,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>thinker-margaret-fuller</t>
+          <t>thinker-mary-wollstonecraft</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -7638,22 +7637,22 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Margaret Fuller</t>
+          <t>Mary Wollstonecraft</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>**Margaret Fuller** · Cambridge, United States · 1810 – 1850 · Humanists and Essayists</t>
+          <t>**Mary Wollstonecraft** · London, England · 1759 – 1797 · Enlightenment Ethics</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Humanists and Essayists</t>
+          <t>Enlightenment Ethics</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>America in the 19th century</t>
+          <t>The Enlightenment</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -7662,12 +7661,12 @@
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Woman in the Nineteenth Century</t>
+          <t>A Vindication of the Rights of Woman</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Fuller</t>
+          <t>Wollstonecraft</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
@@ -7675,8 +7674,10 @@
       <c r="O63" s="2" t="inlineStr"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Fuller was born in Cambridgeport, Massachusetts. Her father, a lawyer, gave her an education as demanding as any boy's: she was translating Virgil from Latin as a small child. By her thirties she was known as the best-read person in New England, and she was the first woman allowed to use Harvard's library.
-From 1839 she ran "Conversations", discussion classes for women who had no access to higher education. Emerson made her the first editor of the Transcendentalist journal *The Dial*. In 1844 she joined the *New-York Tribune* as a critic, the first full-time book reviewer in American journalism.</t>
+          <t>Mary Wollstonecraft was born in 1759 in Spitalfields, London. Her father was a violent man who beat her mother in drunken rages. As a teenager, Mary would lie outside her mother's bedroom door to protect her.
+She had few options as a poor but respectable woman. She ran a school at Newington Green with her sisters and her friend Fanny Blood, then worked as a governess in Ireland. Back in London, the publisher Joseph Johnson gave her work as a translator and reviewer, and she began to live by her pen.
+Her reply to Edmund Burke, *A Vindication of the Rights of Men* (1790), made her famous overnight. Two years later came *A Vindication of the Rights of Woman*. She went to revolutionary Paris, had a daughter with the American Gilbert Imlay, and tried to take her own life after he left her.
+She then married the philosopher William Godwin. She died in 1797, aged 38, eleven days after giving birth to Mary Shelley, the future author of *Frankenstein*.</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -7685,11 +7686,12 @@
       <c r="T63" s="2" t="inlineStr"/>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>Her book *Woman in the Nineteenth Century* (1845) is considered the first major feminist work in the United States. Its key points:
-- **Every path should be open to women** as freely as to men.
-- **Self-reliance is for everyone:** independence praised in men is called a fault in women.
-- **Growth:** people, women and men, are made to expand, not to be held in narrow roles.
-- **Education:** women deserve the same chance to learn and think as men.</t>
+          <t>She believed women seemed weaker than men only because they were denied a real education. Her themes:
+- **Reason has no sex:** men and women are both rational beings and should be treated as such.
+- **Education for all:** girls and boys taught together, in the same way.
+- **Partners, not ornaments:** a wife should be her husband's companion, not property traded in marriage.
+- **Independence:** a woman who depends on others for her body and her bread will soon depend on them for her thoughts.
+- **Liberty makes people better:** freer societies make people wiser and more virtuous, women included.</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr"/>
@@ -7700,14 +7702,15 @@
       <c r="AA63" s="2" t="inlineStr"/>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>In 1846 the *Tribune* sent her to Europe as its first female foreign correspondent. In Italy she joined the side of the 1848 revolutions. During the siege of Rome she volunteered in hospitals, while her partner, Giovanni Ossoli, fought on the walls.
-In 1850 she sailed home with Ossoli and their child. The ship sank off Fire Island, near New York, and all three died; her body was never found. The leaders of the women's suffrage movement later wrote that she had more influence on American women's thinking than any woman before her.</t>
+          <t>Her most famous book was written to change one man's mind. In 1791 the French statesman Talleyrand proposed that girls receive only a domestic education. She also attacked Rousseau, who argued in *Emile* that women should be educated to please men.
+She was not a modern feminist in every way. It is unclear whether she wanted women to vote, she wrote mainly for the middle class, and she could be harsh about the women of her day, calling the frivolous ones spaniels and toys.
+After her death, Godwin published a frank memoir of her unconventional life. It wrecked her reputation for almost a century, until the feminist movement rediscovered her.</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>*Woman in the Nineteenth Century*: bold and still fresh. Free on Project Gutenberg.</t>
+          <t>*A Vindication of the Rights of Woman*: long and passionate, but the opening chapters set out all its main topics. Free on Project Gutenberg; the app quotes her original English.</t>
         </is>
       </c>
       <c r="AE63" s="2" t="inlineStr"/>
@@ -7720,13 +7723,15 @@
       <c r="AL63" s="2" t="inlineStr"/>
       <c r="AM63" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Margaret Fuller": https://en.wikipedia.org/wiki/Margaret_Fuller
-- The app's Fuller thoughts (#293–295), from *Woman in the Nineteenth Century*</t>
+          <t>- Wikipedia, "Mary Wollstonecraft": https://en.wikipedia.org/wiki/Mary_Wollstonecraft
+- Wikipedia, "A Vindication of the Rights of Woman": https://en.wikipedia.org/wiki/A_Vindication_of_the_Rights_of_Woman
+- Stanford Encyclopedia of Philosophy, "Mary Wollstonecraft": https://plato.stanford.edu/entries/wollstonecraft/
+- The app's Wollstonecraft thoughts (#178–179, #192–193), from *A Vindication of the Rights of Woman*</t>
         </is>
       </c>
       <c r="AN63" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO63" s="2" t="inlineStr">
@@ -7739,7 +7744,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>thinker-mary-wollstonecraft</t>
+          <t>thinker-mencius</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7749,22 +7754,22 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Mary Wollstonecraft</t>
+          <t>Mencius</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>**Mary Wollstonecraft** · London, England · 1759 – 1797 · Enlightenment Ethics</t>
+          <t>**Mencius** · Zoucheng, China · about 371 – 289 BCE · Confucianism</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Enlightenment Ethics</t>
+          <t>Confucianism</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>The Enlightenment</t>
+          <t>China of the Hundred Schools</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -7773,39 +7778,36 @@
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>A Vindication of the Rights of Woman</t>
+          <t>human nature, righteousness, the people first</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Wollstonecraft</t>
+          <t>Mengzi, Meng Tzu</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr"/>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>Mary Wollstonecraft was born in 1759 in Spitalfields, London. Her father was a violent man who beat her mother in drunken rages. As a teenager, Mary would lie outside her mother's bedroom door to protect her.
-She had few options as a poor but respectable woman. She ran a school at Newington Green with her sisters and her friend Fanny Blood, then worked as a governess in Ireland. Back in London, the publisher Joseph Johnson gave her work as a translator and reviewer, and she began to live by her pen.
-Her reply to Edmund Burke, *A Vindication of the Rights of Men* (1790), made her famous overnight. Two years later came *A Vindication of the Rights of Woman*. She went to revolutionary Paris, had a daughter with the American Gilbert Imlay, and tried to take her own life after he left her.
-She then married the philosopher William Godwin. She died in 1797, aged 38, eleven days after giving birth to Mary Shelley, the future author of *Frankenstein*.</t>
-        </is>
-      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>Mencius, born Meng Ke, came from the small state of Zou, in eastern China, about a century after Confucius. He lost his father young, and his mother, who raised him, became a model of wise parenting in Chinese tradition. He is said to have studied in the school of Confucius's grandson, Zisi.
+Like Confucius, he spent years travelling from court to court, advising rulers during the violent Warring States period. He served for a time as an official and scholar in the state of Qi, and left to mourn his mother for three years. Disappointed that rulers ignored his advice, he finally withdrew from public life.</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
       <c r="Q64" s="2" t="inlineStr"/>
       <c r="R64" s="2" t="inlineStr"/>
       <c r="S64" s="2" t="inlineStr"/>
-      <c r="T64" s="2" t="inlineStr"/>
-      <c r="U64" s="2" t="inlineStr">
-        <is>
-          <t>She believed women seemed weaker than men only because they were denied a real education. Her themes:
-- **Reason has no sex:** men and women are both rational beings and should be treated as such.
-- **Education for all:** girls and boys taught together, in the same way.
-- **Partners, not ornaments:** a wife should be her husband's companion, not property traded in marriage.
-- **Independence:** a woman who depends on others for her body and her bread will soon depend on them for her thoughts.
-- **Liberty makes people better:** freer societies make people wiser and more virtuous, women included.</t>
-        </is>
-      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>The book named after him, the *Mencius*, records his conversations with rulers and students. His central claim: human nature is good.
+- **Anyone who sees a child about to fall into a well** feels alarm at once, without thinking of reward. That is the seed of goodness in all of us.
+- **Four beginnings:** compassion, shame, respect, and a sense of right and wrong, which we must grow like plants.
+- **Shame matters:** a person without it cannot become good.
+- **Rulers serve the people:** a state that governs humanely will flourish.</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr"/>
       <c r="W64" s="2" t="inlineStr"/>
       <c r="X64" s="2" t="inlineStr"/>
@@ -7814,15 +7816,14 @@
       <c r="AA64" s="2" t="inlineStr"/>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>Her most famous book was written to change one man's mind. In 1791 the French statesman Talleyrand proposed that girls receive only a domestic education. She also attacked Rousseau, who argued in *Emile* that women should be educated to please men.
-She was not a modern feminist in every way. It is unclear whether she wanted women to vote, she wrote mainly for the middle class, and she could be harsh about the women of her day, calling the frivolous ones spaniels and toys.
-After her death, Godwin published a frank memoir of her unconventional life. It wrecked her reputation for almost a century, until the feminist movement rediscovered her.</t>
+          <t>The gentle optimist was also a political radical for his time. He argued that people may overthrow, or even kill, a ruler who ignores their needs and rules harshly, because such a ruler is no longer a true ruler.
+His view of human nature set him against another Confucian, Xunzi, who thought people are born bad. Centuries later, his book became one of the Four Books at the core of Confucian education, and he is honoured as the "Second Sage".</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>*A Vindication of the Rights of Woman*: long and passionate, but the opening chapters set out all its main topics. Free on Project Gutenberg; the app quotes her original English.</t>
+          <t>The *Mencius*, Book II, Part I, with the child at the well. James Legge's 1895 translation is free online.</t>
         </is>
       </c>
       <c r="AE64" s="2" t="inlineStr"/>
@@ -7835,20 +7836,18 @@
       <c r="AL64" s="2" t="inlineStr"/>
       <c r="AM64" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Mary Wollstonecraft": https://en.wikipedia.org/wiki/Mary_Wollstonecraft
-- Wikipedia, "A Vindication of the Rights of Woman": https://en.wikipedia.org/wiki/A_Vindication_of_the_Rights_of_Woman
-- Stanford Encyclopedia of Philosophy, "Mary Wollstonecraft": https://plato.stanford.edu/entries/wollstonecraft/
-- The app's Wollstonecraft thoughts (#178–179, #192–193), from *A Vindication of the Rights of Woman*</t>
+          <t>- Wikipedia, "Mencius": https://en.wikipedia.org/wiki/Mencius
+- The app's Mencius thoughts (#508–512)</t>
         </is>
       </c>
       <c r="AN64" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO64" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages batch 5</t>
+          <t>Thinker pages batch 4</t>
         </is>
       </c>
       <c r="AP64" s="2" t="inlineStr"/>
@@ -7856,7 +7855,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>thinker-mencius</t>
+          <t>thinker-michel-de-montaigne</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -7866,22 +7865,22 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Mencius</t>
+          <t>Michel de Montaigne</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>**Mencius** · Zoucheng, China · about 371 – 289 BCE · Confucianism</t>
+          <t>**Michel de Montaigne** · Saint-Michel-de-Montaigne, France · 1533 – 1592 · Humanists and Essayists</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Confucianism</t>
+          <t>Humanists and Essayists</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>China of the Hundred Schools</t>
+          <t>Renaissance Europe</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
@@ -7890,20 +7889,20 @@
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>human nature, righteousness, the people first</t>
+          <t>Essays, Of Cannibals</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Mengzi, Meng Tzu</t>
+          <t>Montaigne</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Mencius, born Meng Ke, came from the small state of Zou, in eastern China, about a century after Confucius. He lost his father young, and his mother, who raised him, became a model of wise parenting in Chinese tradition. He is said to have studied in the school of Confucius's grandson, Zisi.
-Like Confucius, he spent years travelling from court to court, advising rulers during the violent Warring States period. He served for a time as an official and scholar in the state of Qi, and left to mourn his mother for three years. Disappointed that rulers ignored his advice, he finally withdrew from public life.</t>
+          <t>Montaigne grew up on his family's estate near Bordeaux, in a wealthy family whose fortune began with a herring merchant. His father had an unusual plan for him: Latin was to be his first language, taught by a German tutor who spoke no French.
+He trained in law and worked as a magistrate in Bordeaux, where he met his great friend Étienne de La Boétie. In 1571, on his 38th birthday, he withdrew to a tower of his château, with a library of some 1,500 books. There he began the *Essays*, first published in 1580, and kept adding to them until his death.</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr"/>
@@ -7912,11 +7911,12 @@
       <c r="S65" s="2" t="inlineStr"/>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>The book named after him, the *Mencius*, records his conversations with rulers and students. His central claim: human nature is good.
-- **Anyone who sees a child about to fall into a well** feels alarm at once, without thinking of reward. That is the seed of goodness in all of us.
-- **Four beginnings:** compassion, shame, respect, and a sense of right and wrong, which we must grow like plants.
-- **Shame matters:** a person without it cannot become good.
-- **Rulers serve the people:** a state that governs humanely will flourish.</t>
+          <t>Montaigne's subject was himself, as an example of being human. His big themes:
+- **What do I know?** His famous question: doubt, especially about our own certainties.
+- **Learning to die** is learning to be free.
+- **Living well** is about how we use our time, not how long we live.
+- **Other cultures:** we call barbarous whatever is not our own custom.
+- **Honesty:** to be the same inside as outside.</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr"/>
@@ -7928,14 +7928,14 @@
       <c r="AA65" s="2" t="inlineStr"/>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>The gentle optimist was also a political radical for his time. He argued that people may overthrow, or even kill, a ruler who ignores their needs and rules harshly, because such a ruler is no longer a true ruler.
-His view of human nature set him against another Confucian, Xunzi, who thought people are born bad. Centuries later, his book became one of the Four Books at the core of Confucian education, and he is honoured as the "Second Sage".</t>
+          <t>He wrote in the middle of France's brutal wars between Catholics and Protestants. A Catholic himself, he was trusted by both sides, and acted as a moderating voice between the Catholic king and the Protestant Henry of Navarre.
+From 1578 he suffered from painful kidney stones, and still avoided doctors and drugs. His *Essays*, translated into English in 1603, very likely influenced Shakespeare: a scene in *The Tempest* closely follows one of them.</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>The *Mencius*, Book II, Part I, with the child at the well. James Legge's 1895 translation is free online.</t>
+          <t>"That to Study Philosophy Is to Learn to Die" or "Of Cannibals", two short essays from Book I. Charles Cotton's translation is free on Project Gutenberg.</t>
         </is>
       </c>
       <c r="AE65" s="2" t="inlineStr"/>
@@ -7948,13 +7948,13 @@
       <c r="AL65" s="2" t="inlineStr"/>
       <c r="AM65" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Mencius": https://en.wikipedia.org/wiki/Mencius
-- The app's Mencius thoughts (#508–512)</t>
+          <t>- Wikipedia, "Michel de Montaigne": https://en.wikipedia.org/wiki/Michel_de_Montaigne
+- The app's Montaigne thoughts (#276–285, #303–304), including #277, #278, #281, and #304</t>
         </is>
       </c>
       <c r="AN65" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO65" s="2" t="inlineStr">
@@ -7967,7 +7967,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>thinker-michel-de-montaigne</t>
+          <t>thinker-niccolo-machiavelli</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Michel de Montaigne</t>
+          <t>Niccolò Machiavelli</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>**Michel de Montaigne** · Saint-Michel-de-Montaigne, France · 1533 – 1592 · Humanists and Essayists</t>
+          <t>**Niccolò Machiavelli** · Florence, Italy · 1469 – 1527 · Humanists and Essayists</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -8001,20 +8001,21 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Essays, Of Cannibals</t>
+          <t>The Prince, Discourses on Livy, virtù</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Montaigne</t>
+          <t>Machiavelli</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Montaigne grew up on his family's estate near Bordeaux, in a wealthy family whose fortune began with a herring merchant. His father had an unusual plan for him: Latin was to be his first language, taught by a German tutor who spoke no French.
-He trained in law and worked as a magistrate in Bordeaux, where he met his great friend Étienne de La Boétie. In 1571, on his 38th birthday, he withdrew to a tower of his château, with a library of some 1,500 books. There he began the *Essays*, first published in 1580, and kept adding to them until his death.</t>
+          <t>Machiavelli was born in Florence in 1469. From 1498 to 1512, while the Medici family was out of power, he served the Florentine Republic as a senior official in charge of diplomatic and military affairs. His missions let him watch rulers like Cesare Borgia build states up close.
+He also raised a citizen militia, which took Pisa in 1509. But in 1512 the Medici returned and he lost his post. Wrongly suspected of plotting against them, he was jailed and tortured, then freed under an amnesty three weeks later.
+He retired to his farm outside Florence and became a writer. There, around 1513, he wrote *The Prince*. It was published in 1532, five years after his death.</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr"/>
@@ -8023,12 +8024,12 @@
       <c r="S66" s="2" t="inlineStr"/>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>Montaigne's subject was himself, as an example of being human. His big themes:
-- **What do I know?** His famous question: doubt, especially about our own certainties.
-- **Learning to die** is learning to be free.
-- **Living well** is about how we use our time, not how long we live.
-- **Other cultures:** we call barbarous whatever is not our own custom.
-- **Honesty:** to be the same inside as outside.</t>
+          <t>Machiavelli wanted to describe politics as it is, not as it should be. His themes:
+- **Feared or loved:** if a ruler cannot be both, fear is safer, but he must never be hated.
+- **Appearances:** most people judge by what they see; few know who you really are.
+- **Act early:** problems are easy to cure but hard to see at first, and easy to see but hard to cure later.
+- **Change is hard:** whoever brings a new order makes enemies of all who gained from the old one.
+- **Virtù and fortune:** a ruler's skill and daring matter, and so does fortune, which he must always reckon with.</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr"/>
@@ -8040,14 +8041,14 @@
       <c r="AA66" s="2" t="inlineStr"/>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>He wrote in the middle of France's brutal wars between Catholics and Protestants. A Catholic himself, he was trusted by both sides, and acted as a moderating voice between the Catholic king and the Protestant Henry of Navarre.
-From 1578 he suffered from painful kidney stones, and still avoided doctors and drugs. His *Essays*, translated into English in 1603, very likely influenced Shakespeare: a scene in *The Tempest* closely follows one of them.</t>
+          <t>The man behind "Machiavellian" was a lifelong republican. His *Discourses on Livy* (around 1517) has been called a founding text of modern republicanism. Some 18th-century readers, Rousseau among them, even read *The Prince* as satire, though most scholars disagree.
+Still, the book's hard edges are real. He admired Cesare Borgia and held that fraud, deceit, and violence can be necessary to keep power. In 1559 the Catholic Church put *The Prince* on its list of banned books.</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>"That to Study Philosophy Is to Learn to Die" or "Of Cannibals", two short essays from Book I. Charles Cotton's translation is free on Project Gutenberg.</t>
+          <t>*The Prince*, chapters 15 to 18: the famous pages on how rulers should behave. W. K. Marriott's translation (1908) is free on Project Gutenberg.</t>
         </is>
       </c>
       <c r="AE66" s="2" t="inlineStr"/>
@@ -8060,18 +8061,19 @@
       <c r="AL66" s="2" t="inlineStr"/>
       <c r="AM66" s="2" t="inlineStr">
         <is>
-          <t>- Wikipedia, "Michel de Montaigne": https://en.wikipedia.org/wiki/Michel_de_Montaigne
-- The app's Montaigne thoughts (#276–285, #303–304), including #277, #278, #281, and #304</t>
+          <t>- Stanford Encyclopedia of Philosophy, "Niccolò Machiavelli": https://plato.stanford.edu/entries/machiavelli/
+- Wikipedia, "Niccolò Machiavelli": https://en.wikipedia.org/wiki/Niccol%C3%B2_Machiavelli
+- The app's Machiavelli thoughts (#605–608), from *The Prince*, translated by W. K. Marriott (1908)</t>
         </is>
       </c>
       <c r="AN66" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO66" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages batch 4</t>
+          <t>Thinker pages, batch 6</t>
         </is>
       </c>
       <c r="AP66" s="2" t="inlineStr"/>
@@ -8079,7 +8081,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>thinker-niccolo-machiavelli</t>
+          <t>thinker-nicolas-chamfort</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -8089,12 +8091,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Niccolò Machiavelli</t>
+          <t>Nicolas Chamfort</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>**Niccolò Machiavelli** · Florence, Italy · 1469 – 1527 · Humanists and Essayists</t>
+          <t>**Nicolas Chamfort** · Clermont-Ferrand, France · about 1741 – 1794 · Humanists and Essayists</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -8104,7 +8106,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Renaissance Europe</t>
+          <t>The Enlightenment</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -8113,21 +8115,21 @@
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>The Prince, Discourses on Livy, virtù</t>
+          <t>Maxims and Thoughts, moralists</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Machiavelli</t>
+          <t>Chamfort</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Machiavelli was born in Florence in 1469. From 1498 to 1512, while the Medici family was out of power, he served the Florentine Republic as a senior official in charge of diplomatic and military affairs. His missions let him watch rulers like Cesare Borgia build states up close.
-He also raised a citizen militia, which took Pisa in 1509. But in 1512 the Medici returned and he lost his post. Wrongly suspected of plotting against them, he was jailed and tortured, then freed under an amnesty three weeks later.
-He retired to his farm outside Florence and became a writer. There, around 1513, he wrote *The Prince*. It was published in 1532, five years after his death.</t>
+          <t>Chamfort was born around 1741 in Clermont-Ferrand; sources differ on the date and raised by a grocer. Local tradition said he was the secret child of a noblewoman and a clergyman. At nine he went to Paris on a scholarship, and later lived for years on the hospitality of people who enjoyed his conversation.
+Success came slowly, then all at once. His plays were performed before Louis XVI and Marie Antoinette, he received royal pensions, and in 1781 he was elected to the Académie française. But he disliked court life and kept stepping away from it.
+When the Revolution came, he threw himself into it. He was among the first to enter the Bastille and served as secretary of the Jacobin club. Then his jokes turned on the new rulers, and during the Terror he was jailed. Threatened with arrest again, he tried to take his own life, and he died of his wounds months later, in April 1794.</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr"/>
@@ -8136,12 +8138,12 @@
       <c r="S67" s="2" t="inlineStr"/>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>Machiavelli wanted to describe politics as it is, not as it should be. His themes:
-- **Feared or loved:** if a ruler cannot be both, fear is safer, but he must never be hated.
-- **Appearances:** most people judge by what they see; few know who you really are.
-- **Act early:** problems are easy to cure but hard to see at first, and easy to see but hard to cure later.
-- **Change is hard:** whoever brings a new order makes enemies of all who gained from the old one.
-- **Virtù and fortune:** a ruler's skill and daring matter, and so does fortune, which he must always reckon with.</t>
+          <t>Chamfort left notes of maxims and anecdotes, published after his death as *Maxims and Thoughts*. His themes:
+- **Laughter:** the most wasted day is the one without it.
+- **Society's masks:** he watched the salons and the court closely and showed what lay behind the manners.
+- **Freedom:** he hated servility, whether to a king or to a revolution.
+- **Self-made knowledge:** he joked that he had forgotten what he was taught and only knew what he had guessed.
+- **Books over people:** the great dead, he said, make better company than the living.</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr"/>
@@ -8153,14 +8155,14 @@
       <c r="AA67" s="2" t="inlineStr"/>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>The man behind "Machiavellian" was a lifelong republican. His *Discourses on Livy* (around 1517) has been called a founding text of modern republicanism. Some 18th-century readers, Rousseau among them, even read *The Prince* as satire, though most scholars disagree.
-Still, the book's hard edges are real. He admired Cesare Borgia and held that fraud, deceit, and violence can be necessary to keep power. In 1559 the Catholic Church put *The Prince* on its list of banned books.</t>
+          <t>His wit cost him his life. A republican through and through, he could not stop mocking the revolutionary government, and it was his sarcasm, not royalism, that made him a suspect.
+His maxims are often set beside La Rochefoucauld's. They are less polished but more violent, written in a time of storm. John Stuart Mill praised them highly.</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>*The Prince*, chapters 15 to 18: the famous pages on how rulers should behave. W. K. Marriott's translation (1908) is free on Project Gutenberg.</t>
+          <t>*Maxims and Thoughts*: short and sharp, best read a few at a time. Free in French on Project Gutenberg; the app uses its own translations.</t>
         </is>
       </c>
       <c r="AE67" s="2" t="inlineStr"/>
@@ -8173,19 +8175,19 @@
       <c r="AL67" s="2" t="inlineStr"/>
       <c r="AM67" s="2" t="inlineStr">
         <is>
-          <t>- Stanford Encyclopedia of Philosophy, "Niccolò Machiavelli": https://plato.stanford.edu/entries/machiavelli/
-- Wikipedia, "Niccolò Machiavelli": https://en.wikipedia.org/wiki/Niccol%C3%B2_Machiavelli
-- The app's Machiavelli thoughts (#605–608), from *The Prince*, translated by W. K. Marriott (1908)</t>
+          <t>- Encyclopædia Britannica, "Sébastien-Roch Nicolas Chamfort": https://www.britannica.com/biography/Sebastien-Roch-Nicolas-Chamfort
+- Wikipedia, "Nicolas Chamfort": https://en.wikipedia.org/wiki/Nicolas_Chamfort
+- The app's Chamfort thoughts (#630), from *Maxims and Thoughts*</t>
         </is>
       </c>
       <c r="AN67" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO67" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages, batch 6</t>
+          <t>Thinker pages, batch 7</t>
         </is>
       </c>
       <c r="AP67" s="2" t="inlineStr"/>
@@ -8193,7 +8195,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>thinker-nicolas-chamfort</t>
+          <t>thinker-okakura-kakuzo</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -8203,22 +8205,22 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Nicolas Chamfort</t>
+          <t>Okakura Kakuzō</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>**Nicolas Chamfort** · Clermont-Ferrand, France · about 1741 – 1794 · Humanists and Essayists</t>
+          <t>**Okakura Kakuzō** · Yokohama, Japan · 1863 – 1913 · Japanese Aesthetics</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Humanists and Essayists</t>
+          <t>Japanese Aesthetics</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>The Enlightenment</t>
+          <t>Asia meets the West</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -8227,21 +8229,20 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Maxims and Thoughts, moralists</t>
+          <t>The Book of Tea</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Chamfort</t>
+          <t>Kakuzo Okakura, Okakura Tenshin, Okakura</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Chamfort was born around 1741 in Clermont-Ferrand; sources differ on the date and raised by a grocer. Local tradition said he was the secret child of a noblewoman and a clergyman. At nine he went to Paris on a scholarship, and later lived for years on the hospitality of people who enjoyed his conversation.
-Success came slowly, then all at once. His plays were performed before Louis XVI and Marie Antoinette, he received royal pensions, and in 1781 he was elected to the Académie française. But he disliked court life and kept stepping away from it.
-When the Revolution came, he threw himself into it. He was among the first to enter the Bastille and served as secretary of the Jacobin club. Then his jokes turned on the new rulers, and during the Terror he was jailed. Threatened with arrest again, he tried to take his own life, and he died of his wounds months later, in April 1794.</t>
+          <t>Okakura grew up in Yokohama, studying Western culture at school and Japanese tradition in a Buddhist temple. At the Tokyo Imperial University he studied with the American art historian Ernest Fenollosa, and he went on to work for the Ministry of Education.
+In 1887 he helped found the Tokyo School of Fine Arts, and he soon became its director. When it began to favour European methods, he resigned and started a new academy with leading artists, to learn from Western art without losing Japanese inspiration. From 1906 he worked at the Museum of Fine Arts in Boston, where he became curator of Japanese and Chinese art.</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr"/>
@@ -8250,12 +8251,12 @@
       <c r="S68" s="2" t="inlineStr"/>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>Chamfort left notes of maxims and anecdotes, published after his death as *Maxims and Thoughts*. His themes:
-- **Laughter:** the most wasted day is the one without it.
-- **Society's masks:** he watched the salons and the court closely and showed what lay behind the manners.
-- **Freedom:** he hated servility, whether to a king or to a revolution.
-- **Self-made knowledge:** he joked that he had forgotten what he was taught and only knew what he had guessed.
-- **Books over people:** the great dead, he said, make better company than the living.</t>
+          <t>He wrote his main works in English, to speak directly to Western readers. In *The Book of Tea* (1906), tea becomes a way of seeing life:
+- **The beauty of the imperfect:** true beauty is found by one who completes the incomplete in the mind.
+- **Emptiness is useful:** a pitcher's value lies in the space where water goes.
+- **Leave something unsaid,** so others can finish the thought.
+- **Small things reveal us:** the art of life lies in everyday details.
+- **East and West can complete each other,** if each learns to respect the other.</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr"/>
@@ -8267,14 +8268,14 @@
       <c r="AA68" s="2" t="inlineStr"/>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>His wit cost him his life. A republican through and through, he could not stop mocking the revolutionary government, and it was his sarcasm, not royalism, that made him a suspect.
-His maxims are often set beside La Rochefoucauld's. They are less polished but more violent, written in a time of storm. John Stuart Mill praised them highly.</t>
+          <t>*The Book of Tea* was partly a reply. Written just after the Russo-Japanese War, it protested Western caricatures of Japan, and the fear that Japan was respected only once it adopted the West's taste for war.
+He also spent two years in India and talked with Vivekananda and Tagore, two other voices in the app. In Boston, he once hosted a tea ceremony by candlelight for the art collector Isabella Stewart Gardner.</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>*Maxims and Thoughts*: short and sharp, best read a few at a time. Free in French on Project Gutenberg; the app uses its own translations.</t>
+          <t>*The Book of Tea*, chapter I. Short, warm, and written in English. Free on Project Gutenberg.</t>
         </is>
       </c>
       <c r="AE68" s="2" t="inlineStr"/>
@@ -8287,19 +8288,18 @@
       <c r="AL68" s="2" t="inlineStr"/>
       <c r="AM68" s="2" t="inlineStr">
         <is>
-          <t>- Encyclopædia Britannica, "Sébastien-Roch Nicolas Chamfort": https://www.britannica.com/biography/Sebastien-Roch-Nicolas-Chamfort
-- Wikipedia, "Nicolas Chamfort": https://en.wikipedia.org/wiki/Nicolas_Chamfort
-- The app's Chamfort thoughts (#630), from *Maxims and Thoughts*</t>
+          <t>- Wikipedia, "Okakura Kakuzō": https://en.wikipedia.org/wiki/Okakura_Kakuz%C5%8D
+- The app's Okakura thoughts (#528–537, #550–554), from *The Book of Tea*</t>
         </is>
       </c>
       <c r="AN68" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO68" s="2" t="inlineStr">
         <is>
-          <t>Thinker pages, batch 7</t>
+          <t>Thinker pages batch 4</t>
         </is>
       </c>
       <c r="AP68" s="2" t="inlineStr"/>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AN69" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO69" s="2" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="AN70" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO70" s="2" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AN71" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO71" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="AN72" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO72" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="AN73" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO73" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="AN74" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO74" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="AN75" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO75" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AN76" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO76" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="AN77" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO77" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
         <is>
           <t>- Wikipedia, "Seneca the Younger": https://en.wikipedia.org/wiki/Seneca_the_Younger
 - Stanford Encyclopedia of Philosophy, "Seneca": https://plato.stanford.edu/entries/seneca/
-- Britannica, "Why is Seneca important?": https://www.britannica.com/question/Why-is-Seneca-important</t>
+- Britannica, "Seneca": https://www.britannica.com/biography/Lucius-Annaeus-Seneca-Roman-philosopher-and-statesman</t>
         </is>
       </c>
       <c r="AN78" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO78" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AN79" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO79" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="AN80" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO80" s="2" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="AN81" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO81" s="2" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="AN82" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO82" s="2" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AN83" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO83" s="2" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="AN84" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO84" s="2" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="AN85" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO85" s="2" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="AN86" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO86" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="AN87" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO87" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="AN88" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO88" s="2" t="inlineStr">
@@ -10632,13 +10632,13 @@
       <c r="AM89" s="2" t="inlineStr">
         <is>
           <t>- Wikipedia, "Zhuang Zhou": https://en.wikipedia.org/wiki/Zhuang_Zhou
-- Britannica, "Zhuangzi": https://www.britannica.com/biography/Zhuangzi
+- Britannica, "Zhuangzi": https://www.britannica.com/biography/Zhuang-Zhou
 - Stanford Encyclopedia of Philosophy, "Zhuangzi": https://plato.stanford.edu/entries/zhuangzi/ · The app's thoughts #433 and #437 (Zhuangzi, ch. 5 and 18, Giles translation)</t>
         </is>
       </c>
       <c r="AN89" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO89" s="2" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="AN90" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO90" s="2" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="AN91" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO91" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="AN92" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO92" s="2" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AN93" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO93" s="2" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="AN94" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO94" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="AN95" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO95" s="2" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="AN96" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO96" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AN97" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO97" s="2" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="AN98" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO98" s="2" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="AN99" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO99" s="2" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="AN100" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO100" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="AN101" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO101" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="AN102" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO102" s="2" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="AN103" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO103" s="2" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="AN104" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO104" s="2" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="AN105" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO105" s="2" t="inlineStr">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="AN106" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO106" s="2" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="AN107" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO107" s="2" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AN108" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO108" s="2" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="AN109" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO109" s="2" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="AN110" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO110" s="2" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="AN111" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO111" s="2" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="AN112" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO112" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="AN113" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO113" s="2" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="AN114" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO114" s="2" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="AN115" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO115" s="2" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="AN116" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO116" s="2" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="AN117" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO117" s="2" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="AN118" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO118" s="2" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="AN119" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO119" s="2" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="AN120" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO120" s="2" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="AN121" s="2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="AO121" s="2" t="inlineStr">
@@ -14285,7 +14285,6 @@
           <t>[Varna (Hinduism)](&lt;https://en.wikipedia.org/wiki/Varna_(Hinduism)&gt;) (Wikipedia)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14346,12 +14345,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Encyclopædia Britannica, "Bhagavadgita"</t>
+          <t>Encyclopædia Britannica, "Bhagavad Gita"</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.britannica.com/topic/Bhagavadgita</t>
+          <t>https://www.britannica.com/topic/Bhagavad-Gita</t>
         </is>
       </c>
     </row>
@@ -14995,7 +14994,6 @@
           <t>[Leviathan (Hobbes book)](&lt;https://en.wikipedia.org/wiki/Leviathan_(Hobbes_book)&gt;) (Wikipedia)</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -16011,7 +16009,6 @@
           <t>The app's thought #109 (Aristotle, Nicomachean Ethics, Book II)</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -16058,7 +16055,6 @@
           <t>The app's thoughts #500 and #504 (Analects 12.17 and 13.6)</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -16105,7 +16101,6 @@
           <t>The app's glossary card "Enlightenment Ethics"</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -16237,7 +16232,6 @@
           <t>The app's glossary card "Existential Thought"</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -16641,7 +16635,6 @@
           <t>The app's thought #573 (Sa'di, Gulistan)</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -16705,7 +16698,6 @@
           <t>The app's thought #15 (Epictetus, Enchiridion 1)</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16786,7 +16778,6 @@
           <t>The app's thoughts #410, #422, and #425 (Tao Te Ching 8, 43, and 76)</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -16816,7 +16807,6 @@
           <t>The app's Adam Smith thoughts (#184–186), from *The Theory of Moral Sentiments*</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -16846,7 +16836,6 @@
           <t>The app's al-Ghazali thoughts (#560–561, #578, #600–602), from *The Confessions* and *The Alchemy of Happiness*</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -16893,7 +16882,6 @@
           <t>The app's Aristotle thoughts (#109–120, #126–131, #144–151), including #109, #118, and #129</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -16923,7 +16911,6 @@
           <t>The app's Schopenhauer thoughts (#230–234, #250–253)</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -16953,7 +16940,6 @@
           <t>The app's Spinoza thoughts (#168–172, #190–191), from the *Ethics*</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -16983,7 +16969,6 @@
           <t>The app's Pascal thoughts (#225–229), from the *Pensées*</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -17013,7 +16998,6 @@
           <t>The app's Boethius thoughts (#28–31, #55–57), from *The Consolation of Philosophy*, Book II</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -17060,7 +17044,6 @@
           <t>The app's Confucius thoughts (#467–513), including #467 (Analects 1.1) and #494 (Analects 15.23)</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -17090,7 +17073,6 @@
           <t>The app's Hume thoughts (#173–177, #187–189)</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -17154,7 +17136,6 @@
           <t>The app's Diderot thoughts (#634–635), from *Philosophical Thoughts* and "Regrets on My Old Dressing Gown"</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -17184,7 +17165,6 @@
           <t>The app's Dickinson thoughts (#296–298), from *Poems, Series One*</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -17214,7 +17194,6 @@
           <t>The app's Epictetus thoughts (#15–23, #40–46), including #15, #21, and #42</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -17261,7 +17240,6 @@
           <t>The app's Epicurus thoughts (#58–73, #77–86), including #59 and #73</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -17308,7 +17286,6 @@
           <t>The app's Erasmus thoughts (#290–291), from *The Praise of Folly*</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -17355,7 +17332,6 @@
           <t>The app's Bacon thoughts (#609–610), from the *Essays* (1625)</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -17385,7 +17361,6 @@
           <t>The app's Nietzsche thoughts (#209–216, #245, #256–260), from *Zarathustra*, *The Joyful Wisdom*, *Beyond Good and Evil*, and *Human, All-Too-Human*</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -17415,7 +17390,6 @@
           <t>The app's Dostoevsky thoughts (#217–224, #246–249), from *Notes from Underground* and *The Brothers Karamazov*</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -17462,7 +17436,6 @@
           <t>The app's George Eliot thoughts (#287–289), from *Middlemarch* (1871–1872)</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -17543,7 +17516,6 @@
           <t>The app's Hafiz thoughts (#567–572, #598–599), from the *Divan*, translated by Gertrude Bell (1897)</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -17590,7 +17562,6 @@
           <t>The app's Thoreau thoughts (#266–270), from *Walden*</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -17637,7 +17608,6 @@
           <t>The app's Heraclitus thoughts (#121–125, #132–134), from the *Fragments*, translated by Arthur Fairbanks (1898)</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -17701,7 +17671,6 @@
           <t>The app's Ibn Arabi thoughts (#577), from *The Tarjumán al-Ashwáq*, translated by R. A. Nicholson (1911)</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -17731,7 +17700,6 @@
           <t>The app's Kant thoughts (#152–157, #206–208), from the *Groundwork* and the *Critique of Practical Reason*</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -17778,7 +17746,6 @@
           <t>The app's La Bruyère thoughts (#626–629), from *The Characters*</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -17842,7 +17809,6 @@
           <t>The app's Rousseau thoughts (#617–622), from *The Social Contract*, *Emile*, the *Reveries*, and the *Discourse on Inequality*</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -17889,7 +17855,6 @@
           <t>The app's Locke thoughts (#624–625), from *An Essay Concerning Human Understanding* and the *Second Treatise of Government* (1690)</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17936,37 +17901,40 @@
           <t>The app's Mill thoughts (#158–167, #197–205), including #158, #160, #164, and #197</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>thinker-kakuzo-okakura</t>
+          <t>thinker-kamo-no-chomei</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Wikipedia, "Okakura Kakuzō"</t>
+          <t>Wikipedia, "Kamo no Chōmei"</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Okakura_Kakuz%C5%8D</t>
+          <t>https://en.wikipedia.org/wiki/Kamo_no_Ch%C5%8Dmei</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>thinker-kakuzo-okakura</t>
+          <t>thinker-kamo-no-chomei</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>The app's Okakura thoughts (#528–537, #550–554), from *The Book of Tea*</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr"/>
+          <t>Wikipedia, "Hōjōki"</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/H%C5%8Dj%C5%8Dki</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -17976,44 +17944,43 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Wikipedia, "Kamo no Chōmei"</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Kamo_no_Ch%C5%8Dmei</t>
+          <t>The app's Chōmei thoughts (#538–541), from *Hōjōki*</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>thinker-kamo-no-chomei</t>
+          <t>thinker-kenko</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Wikipedia, "Hōjōki"</t>
+          <t>Wikipedia, "Yoshida Kenkō"</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/H%C5%8Dj%C5%8Dki</t>
+          <t>https://en.wikipedia.org/wiki/Yoshida_Kenk%C5%8D</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>thinker-kamo-no-chomei</t>
+          <t>thinker-kenko</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>The app's Chōmei thoughts (#538–541), from *Hōjōki*</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr"/>
+          <t>Wikipedia, "Tsurezuregusa"</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tsurezuregusa</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -18023,44 +17990,43 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Wikipedia, "Yoshida Kenkō"</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Yoshida_Kenk%C5%8D</t>
+          <t>The app's Kenkō thoughts (#515–527, #546–547) and their translations</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>thinker-kenko</t>
+          <t>thinker-la-rochefoucauld</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Wikipedia, "Tsurezuregusa"</t>
+          <t>Wikipedia, "François de La Rochefoucauld (writer)"</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tsurezuregusa</t>
+          <t>https://en.wikipedia.org/wiki/Fran%C3%A7ois_de_La_Rochefoucauld_(writer)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>thinker-kenko</t>
+          <t>thinker-la-rochefoucauld</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>The app's Kenkō thoughts (#515–527, #546–547) and their translations</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
+          <t>Wikipedia, "French moralists"</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/French_moralists</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -18070,44 +18036,43 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Wikipedia, "François de La Rochefoucauld (writer)"</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Fran%C3%A7ois_de_La_Rochefoucauld_(writer)</t>
+          <t>The app's La Rochefoucauld thoughts (#271–275, #286, #299–302), from the *Maxims*</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>thinker-la-rochefoucauld</t>
+          <t>thinker-laozi</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Wikipedia, "French moralists"</t>
+          <t>Wikipedia, "Laozi"</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/French_moralists</t>
+          <t>https://en.wikipedia.org/wiki/Laozi</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>thinker-la-rochefoucauld</t>
+          <t>thinker-laozi</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>The app's La Rochefoucauld thoughts (#271–275, #286, #299–302), from the *Maxims*</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr"/>
+          <t>Wikipedia, "Tao Te Ching"</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tao_Te_Ching</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -18117,44 +18082,43 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Wikipedia, "Laozi"</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Laozi</t>
+          <t>The app's Laozi thoughts (#410–428, #441–451), including #410, #422, and #442</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>thinker-laozi</t>
+          <t>thinker-leo-tolstoy</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Wikipedia, "Tao Te Ching"</t>
+          <t>Encyclopædia Britannica, "Leo Tolstoy"</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Tao_Te_Ching</t>
+          <t>https://www.britannica.com/biography/Leo-Tolstoy</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>thinker-laozi</t>
+          <t>thinker-leo-tolstoy</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>The app's Laozi thoughts (#410–428, #441–451), including #410, #422, and #442</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr"/>
+          <t>Wikipedia, "Leo Tolstoy"</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Leo_Tolstoy</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -18164,12 +18128,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Encyclopædia Britannica, "Leo Tolstoy"</t>
+          <t>Wikipedia, "A Confession"</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://www.britannica.com/biography/Leo-Tolstoy</t>
+          <t>https://en.wikipedia.org/wiki/A_Confession</t>
         </is>
       </c>
     </row>
@@ -18181,74 +18145,72 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Wikipedia, "Leo Tolstoy"</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Leo_Tolstoy</t>
+          <t>The app's Tolstoy thoughts (#243–244), from *A Confession*, translated by Aylmer Maude</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>thinker-leo-tolstoy</t>
+          <t>thinker-lucretius</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Wikipedia, "A Confession"</t>
+          <t>Wikipedia, "Lucretius"</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/A_Confession</t>
+          <t>https://en.wikipedia.org/wiki/Lucretius</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>thinker-leo-tolstoy</t>
+          <t>thinker-lucretius</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>The app's Tolstoy thoughts (#243–244), from *A Confession*, translated by Aylmer Maude</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
+          <t>The app's Lucretius thoughts (#74–76, #87–94), from *On the Nature of Things*</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>thinker-lucretius</t>
+          <t>thinker-marcus-aurelius</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Wikipedia, "Lucretius"</t>
+          <t>Wikipedia, "Marcus Aurelius"</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lucretius</t>
+          <t>https://en.wikipedia.org/wiki/Marcus_Aurelius</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>thinker-lucretius</t>
+          <t>thinker-marcus-aurelius</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>The app's Lucretius thoughts (#74–76, #87–94), from *On the Nature of Things*</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr"/>
+          <t>Wikipedia, "Meditations"</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Meditations</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -18258,74 +18220,72 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Wikipedia, "Marcus Aurelius"</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/Marcus_Aurelius</t>
+          <t>The app's Marcus Aurelius thoughts (#1–14, #32–39), including #32 (Meditations 2.1)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>thinker-marcus-aurelius</t>
+          <t>thinker-margaret-fuller</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Wikipedia, "Meditations"</t>
+          <t>Wikipedia, "Margaret Fuller"</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Meditations</t>
+          <t>https://en.wikipedia.org/wiki/Margaret_Fuller</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>thinker-marcus-aurelius</t>
+          <t>thinker-margaret-fuller</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>The app's Marcus Aurelius thoughts (#1–14, #32–39), including #32 (Meditations 2.1)</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr"/>
+          <t>The app's Fuller thoughts (#293–295), from *Woman in the Nineteenth Century*</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>thinker-margaret-fuller</t>
+          <t>thinker-mary-wollstonecraft</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Wikipedia, "Margaret Fuller"</t>
+          <t>Wikipedia, "Mary Wollstonecraft"</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Margaret_Fuller</t>
+          <t>https://en.wikipedia.org/wiki/Mary_Wollstonecraft</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>thinker-margaret-fuller</t>
+          <t>thinker-mary-wollstonecraft</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>The app's Fuller thoughts (#293–295), from *Woman in the Nineteenth Century*</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr"/>
+          <t>Wikipedia, "A Vindication of the Rights of Woman"</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/A_Vindication_of_the_Rights_of_Woman</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -18335,12 +18295,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Wikipedia, "Mary Wollstonecraft"</t>
+          <t>Stanford Encyclopedia of Philosophy, "Mary Wollstonecraft"</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Mary_Wollstonecraft</t>
+          <t>https://plato.stanford.edu/entries/wollstonecraft/</t>
         </is>
       </c>
     </row>
@@ -18352,104 +18312,101 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Wikipedia, "A Vindication of the Rights of Woman"</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/A_Vindication_of_the_Rights_of_Woman</t>
+          <t>The app's Wollstonecraft thoughts (#178–179, #192–193), from *A Vindication of the Rights of Woman*</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>thinker-mary-wollstonecraft</t>
+          <t>thinker-mencius</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Stanford Encyclopedia of Philosophy, "Mary Wollstonecraft"</t>
+          <t>Wikipedia, "Mencius"</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://plato.stanford.edu/entries/wollstonecraft/</t>
+          <t>https://en.wikipedia.org/wiki/Mencius</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>thinker-mary-wollstonecraft</t>
+          <t>thinker-mencius</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>The app's Wollstonecraft thoughts (#178–179, #192–193), from *A Vindication of the Rights of Woman*</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr"/>
+          <t>The app's Mencius thoughts (#508–512)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>thinker-mencius</t>
+          <t>thinker-michel-de-montaigne</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Wikipedia, "Mencius"</t>
+          <t>Wikipedia, "Michel de Montaigne"</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Mencius</t>
+          <t>https://en.wikipedia.org/wiki/Michel_de_Montaigne</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>thinker-mencius</t>
+          <t>thinker-michel-de-montaigne</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>The app's Mencius thoughts (#508–512)</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr"/>
+          <t>The app's Montaigne thoughts (#276–285, #303–304), including #277, #278, #281, and #304</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>thinker-michel-de-montaigne</t>
+          <t>thinker-niccolo-machiavelli</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Wikipedia, "Michel de Montaigne"</t>
+          <t>Stanford Encyclopedia of Philosophy, "Niccolò Machiavelli"</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Michel_de_Montaigne</t>
+          <t>https://plato.stanford.edu/entries/machiavelli/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>thinker-michel-de-montaigne</t>
+          <t>thinker-niccolo-machiavelli</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>The app's Montaigne thoughts (#276–285, #303–304), including #277, #278, #281, and #304</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr"/>
+          <t>Wikipedia, "Niccolò Machiavelli"</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Niccol%C3%B2_Machiavelli</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -18459,44 +18416,43 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Stanford Encyclopedia of Philosophy, "Niccolò Machiavelli"</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>https://plato.stanford.edu/entries/machiavelli/</t>
+          <t>The app's Machiavelli thoughts (#605–608), from *The Prince*, translated by W. K. Marriott (1908)</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>thinker-niccolo-machiavelli</t>
+          <t>thinker-nicolas-chamfort</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Wikipedia, "Niccolò Machiavelli"</t>
+          <t>Encyclopædia Britannica, "Sébastien-Roch Nicolas Chamfort"</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Niccol%C3%B2_Machiavelli</t>
+          <t>https://www.britannica.com/biography/Sebastien-Roch-Nicolas-Chamfort</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>thinker-niccolo-machiavelli</t>
+          <t>thinker-nicolas-chamfort</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>The app's Machiavelli thoughts (#605–608), from *The Prince*, translated by W. K. Marriott (1908)</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr"/>
+          <t>Wikipedia, "Nicolas Chamfort"</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nicolas_Chamfort</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -18506,44 +18462,38 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Encyclopædia Britannica, "Sébastien-Roch Nicolas Chamfort"</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>https://www.britannica.com/biography/Sebastien-Roch-Nicolas-Chamfort</t>
+          <t>The app's Chamfort thoughts (#630), from *Maxims and Thoughts*</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>thinker-nicolas-chamfort</t>
+          <t>thinker-okakura-kakuzo</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Wikipedia, "Nicolas Chamfort"</t>
+          <t>Wikipedia, "Okakura Kakuzō"</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Nicolas_Chamfort</t>
+          <t>https://en.wikipedia.org/wiki/Okakura_Kakuz%C5%8D</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>thinker-nicolas-chamfort</t>
+          <t>thinker-okakura-kakuzo</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>The app's Chamfort thoughts (#630), from *Maxims and Thoughts*</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr"/>
+          <t>The app's Okakura thoughts (#528–537, #550–554), from *The Book of Tea*</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -18573,7 +18523,6 @@
           <t>The app's Omar Khayyam thoughts (#579–586), from FitzGerald's *Rubáiyát*</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -18620,7 +18569,6 @@
           <t>The app's Petrarch thoughts (#292), from *Petrarch's Secret*, translated by William H. Draper (1911)</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -18650,7 +18598,6 @@
           <t>The app's Plato thoughts (#95–108, #135–143), including #95, #96, #105, #106, and #108</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -18697,7 +18644,6 @@
           <t>The app's Tagore thoughts (#374–379, #385–400), from *Sadhana* and *Stray Birds*</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -18744,7 +18690,6 @@
           <t>The app's Emerson thoughts (#261–265, #305–306), from "Self-Reliance" and "Compensation" (1841)</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -18791,7 +18736,6 @@
           <t>The app's Descartes thoughts (#180–183), from *Discourse on Method*, translated by John Veitch (1850)</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -18821,7 +18765,6 @@
           <t>The app's Rumi thoughts (#555–559, #562–566, #593–597, #603–604), from the *Masnavi* and the *Divani Shamsi Tabriz*</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -18851,7 +18794,6 @@
           <t>The app's Sa'di thoughts (#573–576, #587–592), from the *Gulistan*</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -18915,7 +18857,6 @@
           <t>The app's Sei Shōnagon thoughts (#542–545, #548–549), from *The Pillow Book*, translated by W. G. Aston (1899)</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -18959,12 +18900,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Britannica, "Why is Seneca important?"</t>
+          <t>Britannica, "Seneca"</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://www.britannica.com/question/Why-is-Seneca-important</t>
+          <t>https://www.britannica.com/biography/Lucius-Annaeus-Seneca-Roman-philosopher-and-statesman</t>
         </is>
       </c>
     </row>
@@ -18996,7 +18937,6 @@
           <t>The app's Simone Weil thoughts (#235–238, #254–255)</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -19026,7 +18966,6 @@
           <t>The app's Vivekananda thoughts (#380–384, #404–408), from *Karma-Yoga*</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -19056,7 +18995,6 @@
           <t>The app's Gita thoughts (#360–362, #368–372, #401–403)</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -19103,7 +19041,6 @@
           <t>The app's Dhammapada thoughts (#307–336 and others), from Müller's translation</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -19201,7 +19138,6 @@
           <t>The app's thought from this text (#355), translated by T. W. Rhys Davids (1890)</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -19231,7 +19167,6 @@
           <t>The app's Upanishad thoughts (#363–367, #373, #409), from the *Katha*, *Isha*, *Brihadaranyaka*, and *Mundaka*</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -19278,7 +19213,6 @@
           <t>The app's Hobbes thoughts (#623), from *Leviathan* (1651)</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -19325,7 +19259,6 @@
           <t>The app's Vauvenargues thoughts (#631–633), from *Reflections and Maxims*</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -19355,7 +19288,6 @@
           <t>The app's Voltaire thoughts (#611–616), from *Candide*, *Zadig*, and the *Philosophical Dictionary*</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -19385,7 +19317,6 @@
           <t>The app's William James thoughts (#239–242), from *The Will to Believe*</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -19417,7 +19348,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>https://www.britannica.com/biography/Zhuangzi</t>
+          <t>https://www.britannica.com/biography/Zhuang-Zhou</t>
         </is>
       </c>
     </row>
@@ -19449,7 +19380,6 @@
           <t>The app's thoughts #433 and #437 (Zhuangzi, ch. 5 and 18, Giles translation)</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -19530,7 +19460,6 @@
           <t>The app's thoughts #177, #188, #259, #264, #421, #525, #533, and #534, with their sources</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -19543,7 +19472,6 @@
           <t>The app's thoughts #18, #33, #88, #121, #209, #345, #515, #517, and #529, with their sources</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -19607,7 +19535,6 @@
           <t>The app's thoughts #109, #113, #119, #154, #155, #208, #328, #333, #339, #357, #475, #487, #492, #495, and #504, with their sources</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -19620,7 +19547,6 @@
           <t>The app's thoughts #4, #59, #73, #75, #170, #277, #387, #437, #520, #582, and #583, with their sources</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -19718,7 +19644,6 @@
           <t>The app's thoughts listed above, with their sources</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -19731,7 +19656,6 @@
           <t>The app's thoughts #5, #25, #41, #61, #72, #182, #194, #254, #267, #268, #353, #368, #370, and #419, with their sources</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -19846,7 +19770,6 @@
           <t>The app's thoughts listed above, with their sources</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -19859,7 +19782,6 @@
           <t>The app's thoughts #23, #44, #290, #301, #410, #411, #415, #468, #483, and #490, with their sources</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -19923,7 +19845,6 @@
           <t>The app's thoughts listed above, with their sources</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -20004,7 +19925,6 @@
           <t>The app's thoughts listed above, with their sources</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -20085,7 +20005,6 @@
           <t>The app's thoughts #15, #42, #168, #197, #198, and the others listed above, with their sources</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -20183,7 +20102,6 @@
           <t>The app's thoughts #58, #112, #115, #117, #211, #280, #502, #503, #511, and #512, with their sources</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -20196,7 +20114,6 @@
           <t>The app's thoughts #22, #40, #109, #174, #311, #314, #338, #413, #432, #495, #514, and #527, with their sources</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -20226,7 +20143,6 @@
           <t>The app's thoughts #58, #64, #66, #67, #110, #116, #155, #158, #159, #331, and #479, with their sources</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -20324,7 +20240,6 @@
           <t>The app's thoughts #71, #84, #85, #98, #127–129, #135, #491, #500, #504, and #617, with their sources</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -20422,7 +20337,6 @@
           <t>The app's thoughts listed above, with their sources</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -20469,7 +20383,6 @@
           <t>The app's thoughts listed above, with their sources</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -20516,7 +20429,6 @@
           <t>The app's thoughts #96, #97, #104, #162, #167, #175, #418, #420, #429, #470, #471, #480, and #482, with their sources</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -20546,7 +20458,6 @@
           <t>The app's thoughts #106, #219, #221, #280, #308, #378, #389, #559, #567, and #577, with their sources</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -20610,7 +20521,6 @@
           <t>The app's thoughts #7, #9, #111, #168, #169, #173, #228, #307, #308, and #315, with their sources</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -20657,7 +20567,6 @@
           <t>The app's thoughts #37, #44, #87, #89, #152, #226, #410, #422, #441, #543, and #553, with their sources</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -20670,7 +20579,6 @@
           <t>The app's thoughts #116, #144, #163, #166, #214, #240, #243, #288, #296, #385, and #434, with their sources</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -20700,7 +20608,6 @@
           <t>The app's thoughts #95, #214, #273, #283, #355, #364, #366, #493, and #513, with their sources</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -20713,7 +20620,6 @@
           <t>The app's thoughts #3, #215, #225, #229, #230, #354, #417, #438, #522, and #541, with their sources</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -20726,7 +20632,6 @@
           <t>The app's thoughts #6, #17, #28, #199, #213, #236, #248, #380, #555, #570, and #596, with their sources</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -20875,7 +20780,6 @@
           <t>The app's thoughts listed above, with their sources</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -20888,7 +20792,6 @@
           <t>The app's thoughts #24, #26, #43, #63, #77, #79, #227, #278, #520, #579, and #583, with their sources</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -20952,7 +20855,6 @@
           <t>The app's thoughts listed above, with their sources</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -21033,7 +20935,6 @@
           <t>The app's thoughts listed above, with their sources</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -21046,7 +20947,6 @@
           <t>The app's thoughts #10, #12, #360, #368, #381, #432, #449, #472, and #611, with their sources</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -21093,7 +20993,6 @@
           <t>The app's thoughts listed above, with their sources</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
